--- a/base/pacotes/pacote-piloto/executivo-pacote-piloto.xlsx
+++ b/base/pacotes/pacote-piloto/executivo-pacote-piloto.xlsx
@@ -83,7 +83,7 @@
       <sz val="9"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -110,8 +110,26 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00E8F8F5"/>
+        <bgColor rgb="00E8F8F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FEF9E7"/>
+        <bgColor rgb="00FEF9E7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00EAEDED"/>
         <bgColor rgb="00EAEDED"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FADBD8"/>
+        <bgColor rgb="00FADBD8"/>
       </patternFill>
     </fill>
   </fills>
@@ -141,48 +159,78 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -200,6 +248,9 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
     <xf numFmtId="4" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -209,7 +260,16 @@
     <xf numFmtId="165" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -578,16 +638,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -600,7 +662,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Gerado em 2026-04-13T08:13:16 | AC=15000 m² | UR=90 | baseado em 5 projetos similares</t>
+          <t>Gerado em 2026-04-13T17:08:36 | AC=15000 m² | UR=90 | baseado em 5 projetos similares</t>
         </is>
       </c>
     </row>
@@ -640,6 +702,16 @@
           <t>Confiança</t>
         </is>
       </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Fonte total</t>
+        </is>
+      </c>
+      <c r="I4" s="3" t="inlineStr">
+        <is>
+          <t>P10-P90 ref</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
@@ -657,14 +729,24 @@
         <v>247.40452</v>
       </c>
       <c r="E5" s="8" t="n">
-        <v>0.077194571148295</v>
+        <v>0.07180388697421142</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G5" s="4" t="inlineStr">
         <is>
           <t>🟢 Alta</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
+          <t>calibrado (n=131)</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="inlineStr">
+        <is>
+          <t>61–942</t>
         </is>
       </c>
     </row>
@@ -678,13 +760,13 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>354844.05</v>
+        <v>322585.5</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>23.65627</v>
+        <v>21.5057</v>
       </c>
       <c r="E6" s="8" t="n">
-        <v>0.007381173220352954</v>
+        <v>0.006241570898144053</v>
       </c>
       <c r="F6" s="4" t="n">
         <v>0</v>
@@ -692,6 +774,16 @@
       <c r="G6" s="4" t="inlineStr">
         <is>
           <t>🟢 Alta</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>calibrado (n=58)</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
+          <t>6–145</t>
         </is>
       </c>
     </row>
@@ -705,13 +797,13 @@
         </is>
       </c>
       <c r="C7" s="6" t="n">
-        <v>3228418.05</v>
+        <v>3081671.775</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>215.22787</v>
+        <v>205.444785</v>
       </c>
       <c r="E7" s="8" t="n">
-        <v>0.06715488918234391</v>
+        <v>0.05962596852143673</v>
       </c>
       <c r="F7" s="4" t="n">
         <v>1</v>
@@ -719,6 +811,16 @@
       <c r="G7" s="4" t="inlineStr">
         <is>
           <t>🟢 Alta</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
+          <t>calibrado (n=63)</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="inlineStr">
+        <is>
+          <t>82–318</t>
         </is>
       </c>
     </row>
@@ -732,20 +834,30 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>10843093.8</v>
+        <v>10350225.9</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>722.87292</v>
+        <v>690.0150600000001</v>
       </c>
       <c r="E8" s="8" t="n">
-        <v>0.2255490928545516</v>
+        <v>0.2002621592311398</v>
       </c>
       <c r="F8" s="4" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
           <t>🟢 Alta</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>calibrado (n=56)</t>
+        </is>
+      </c>
+      <c r="I8" s="4" t="inlineStr">
+        <is>
+          <t>405–793</t>
         </is>
       </c>
     </row>
@@ -765,7 +877,7 @@
         <v>167.26248</v>
       </c>
       <c r="E9" s="8" t="n">
-        <v>0.05218884203409166</v>
+        <v>0.04854436858690495</v>
       </c>
       <c r="F9" s="4" t="n">
         <v>1</v>
@@ -773,6 +885,16 @@
       <c r="G9" s="4" t="inlineStr">
         <is>
           <t>🟢 Alta</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>calibrado (n=130)</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="inlineStr">
+        <is>
+          <t>92–320</t>
         </is>
       </c>
     </row>
@@ -786,13 +908,13 @@
         </is>
       </c>
       <c r="C10" s="6" t="n">
-        <v>1009663.05</v>
+        <v>963769.2749999999</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>67.31087000000001</v>
+        <v>64.251285</v>
       </c>
       <c r="E10" s="8" t="n">
-        <v>0.02100217790389859</v>
+        <v>0.01864756555817107</v>
       </c>
       <c r="F10" s="4" t="n">
         <v>0</v>
@@ -800,6 +922,16 @@
       <c r="G10" s="4" t="inlineStr">
         <is>
           <t>🟢 Alta</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>calibrado (n=61)</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t>35–577</t>
         </is>
       </c>
     </row>
@@ -813,13 +945,13 @@
         </is>
       </c>
       <c r="C11" s="6" t="n">
-        <v>4548396.600000001</v>
+        <v>4961887.199999999</v>
       </c>
       <c r="D11" s="7" t="n">
-        <v>303.22644</v>
+        <v>330.79248</v>
       </c>
       <c r="E11" s="8" t="n">
-        <v>0.09461199414070612</v>
+        <v>0.09600546443468004</v>
       </c>
       <c r="F11" s="4" t="n">
         <v>30</v>
@@ -829,31 +961,51 @@
           <t>🟢 Alta</t>
         </is>
       </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>calibrado (n=80)</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t>28–447</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="n">
+      <c r="A12" s="9" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Sistemas Especiais</t>
         </is>
       </c>
-      <c r="C12" s="6" t="n">
+      <c r="C12" s="11" t="n">
         <v>1665015.145092665</v>
       </c>
-      <c r="D12" s="7" t="n">
+      <c r="D12" s="12" t="n">
         <v>111.0010096728443</v>
       </c>
-      <c r="E12" s="8" t="n">
-        <v>0.03463427159181636</v>
-      </c>
-      <c r="F12" s="4" t="n">
+      <c r="E12" s="13" t="n">
+        <v>0.03221567638526678</v>
+      </c>
+      <c r="F12" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="G12" s="4" t="inlineStr">
+      <c r="G12" s="9" t="inlineStr">
         <is>
           <t>🟡 Média</t>
+        </is>
+      </c>
+      <c r="H12" s="9" t="inlineStr">
+        <is>
+          <t>similares (n=1)</t>
+        </is>
+      </c>
+      <c r="I12" s="9" t="inlineStr">
+        <is>
+          <t>111–111</t>
         </is>
       </c>
     </row>
@@ -867,13 +1019,13 @@
         </is>
       </c>
       <c r="C13" s="6" t="n">
-        <v>647547.4500000001</v>
+        <v>765283.35</v>
       </c>
       <c r="D13" s="7" t="n">
-        <v>43.16983</v>
+        <v>51.01889</v>
       </c>
       <c r="E13" s="8" t="n">
-        <v>0.0134697478986835</v>
+        <v>0.01480714503966914</v>
       </c>
       <c r="F13" s="4" t="n">
         <v>30</v>
@@ -881,6 +1033,16 @@
       <c r="G13" s="4" t="inlineStr">
         <is>
           <t>🟢 Alta</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>calibrado (n=18)</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="inlineStr">
+        <is>
+          <t>23–125</t>
         </is>
       </c>
     </row>
@@ -894,20 +1056,30 @@
         </is>
       </c>
       <c r="C14" s="6" t="n">
-        <v>1547726.4</v>
+        <v>1829131.2</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>103.18176</v>
+        <v>121.94208</v>
       </c>
       <c r="E14" s="8" t="n">
-        <v>0.03219452786685667</v>
+        <v>0.03539108877121665</v>
       </c>
       <c r="F14" s="4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
           <t>🟢 Alta</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>calibrado (n=61)</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t>38–899</t>
         </is>
       </c>
     </row>
@@ -921,13 +1093,13 @@
         </is>
       </c>
       <c r="C15" s="6" t="n">
-        <v>1040659.95</v>
+        <v>1182568.125</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>69.37733000000001</v>
+        <v>78.837875</v>
       </c>
       <c r="E15" s="8" t="n">
-        <v>0.02164694984862743</v>
+        <v>0.02288101230239047</v>
       </c>
       <c r="F15" s="4" t="n">
         <v>0</v>
@@ -935,6 +1107,16 @@
       <c r="G15" s="4" t="inlineStr">
         <is>
           <t>🟢 Alta</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>calibrado (n=35)</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t>34–119</t>
         </is>
       </c>
     </row>
@@ -948,13 +1130,13 @@
         </is>
       </c>
       <c r="C16" s="6" t="n">
-        <v>3330978.75</v>
+        <v>4239427.5</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>222.06525</v>
+        <v>282.6285</v>
       </c>
       <c r="E16" s="8" t="n">
-        <v>0.06928827226232132</v>
+        <v>0.08202689615246686</v>
       </c>
       <c r="F16" s="4" t="n">
         <v>0</v>
@@ -962,6 +1144,16 @@
       <c r="G16" s="4" t="inlineStr">
         <is>
           <t>🟢 Alta</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>calibrado (n=42)</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="inlineStr">
+        <is>
+          <t>125–638</t>
         </is>
       </c>
     </row>
@@ -975,13 +1167,13 @@
         </is>
       </c>
       <c r="C17" s="6" t="n">
-        <v>2062186.5</v>
+        <v>2249658</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>137.4791</v>
+        <v>149.9772</v>
       </c>
       <c r="E17" s="8" t="n">
-        <v>0.04289590249342884</v>
+        <v>0.04352768460943518</v>
       </c>
       <c r="F17" s="4" t="n">
         <v>0</v>
@@ -989,6 +1181,16 @@
       <c r="G17" s="4" t="inlineStr">
         <is>
           <t>🟢 Alta</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>calibrado (n=61)</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="inlineStr">
+        <is>
+          <t>60–193</t>
         </is>
       </c>
     </row>
@@ -1002,13 +1204,13 @@
         </is>
       </c>
       <c r="C18" s="6" t="n">
-        <v>5083755.600000001</v>
+        <v>6470234.399999999</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>338.91704</v>
+        <v>431.34896</v>
       </c>
       <c r="E18" s="8" t="n">
-        <v>0.1057480904457588</v>
+        <v>0.1251898387720792</v>
       </c>
       <c r="F18" s="4" t="n">
         <v>7</v>
@@ -1016,6 +1218,16 @@
       <c r="G18" s="4" t="inlineStr">
         <is>
           <t>🟢 Alta</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>calibrado (n=56)</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="inlineStr">
+        <is>
+          <t>235–548</t>
         </is>
       </c>
     </row>
@@ -1029,13 +1241,13 @@
         </is>
       </c>
       <c r="C19" s="6" t="n">
-        <v>549710.7000000001</v>
+        <v>749605.5000000001</v>
       </c>
       <c r="D19" s="7" t="n">
-        <v>36.64738000000001</v>
+        <v>49.97370000000001</v>
       </c>
       <c r="E19" s="8" t="n">
-        <v>0.01143462852986115</v>
+        <v>0.01450380092685109</v>
       </c>
       <c r="F19" s="4" t="n">
         <v>30</v>
@@ -1043,6 +1255,16 @@
       <c r="G19" s="4" t="inlineStr">
         <is>
           <t>🟢 Alta</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>calibrado (n=21)</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t>23–518</t>
         </is>
       </c>
     </row>
@@ -1056,13 +1278,13 @@
         </is>
       </c>
       <c r="C20" s="6" t="n">
-        <v>2218817.7</v>
+        <v>2723094.45</v>
       </c>
       <c r="D20" s="7" t="n">
-        <v>147.92118</v>
+        <v>181.53963</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>0.04615401551212465</v>
+        <v>0.05268800696874965</v>
       </c>
       <c r="F20" s="4" t="n">
         <v>0</v>
@@ -1070,6 +1292,16 @@
       <c r="G20" s="4" t="inlineStr">
         <is>
           <t>🟢 Alta</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>calibrado (n=33)</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t>68–253</t>
         </is>
       </c>
     </row>
@@ -1083,13 +1315,13 @@
         </is>
       </c>
       <c r="C21" s="6" t="n">
-        <v>2883772.65</v>
+        <v>3145933.8</v>
       </c>
       <c r="D21" s="7" t="n">
-        <v>192.25151</v>
+        <v>209.72892</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>0.05998585986651396</v>
+        <v>0.06086934736238217</v>
       </c>
       <c r="F21" s="4" t="n">
         <v>30</v>
@@ -1097,6 +1329,16 @@
       <c r="G21" s="4" t="inlineStr">
         <is>
           <t>🟢 Alta</t>
+        </is>
+      </c>
+      <c r="H21" s="4" t="inlineStr">
+        <is>
+          <t>calibrado (n=57)</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="inlineStr">
+        <is>
+          <t>70–365</t>
         </is>
       </c>
     </row>
@@ -1110,13 +1352,13 @@
         </is>
       </c>
       <c r="C22" s="6" t="n">
-        <v>839615.7000000002</v>
+        <v>763287</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>55.97438000000001</v>
+        <v>50.8858</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>0.01746499319976734</v>
+        <v>0.01476851850480471</v>
       </c>
       <c r="F22" s="4" t="n">
         <v>0</v>
@@ -1126,27 +1368,65 @@
           <t>🟢 Alta</t>
         </is>
       </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>calibrado (n=23)</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t>39–95</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="B23" s="9" t="inlineStr">
+      <c r="B23" s="14" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="C23" s="10" t="n">
-        <v>48074207.09509268</v>
-      </c>
-      <c r="D23" s="11" t="n">
-        <v>3204.947139672845</v>
-      </c>
-      <c r="E23" s="12" t="n">
-        <v>1</v>
+      <c r="C23" s="15" t="n">
+        <v>51683383.12009267</v>
+      </c>
+      <c r="D23" s="16" t="n">
+        <v>3445.558874672844</v>
+      </c>
+      <c r="E23" s="17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="18" t="inlineStr">
+        <is>
+          <t>Legenda fonte:</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="19" t="inlineStr">
+        <is>
+          <t>🟢 calibrado = base V2 calibration-indices.json</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="20" t="inlineStr">
+        <is>
+          <t>🟡 similares = mediana dos 5 projetos similares</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="21" t="inlineStr">
+        <is>
+          <t>🔴 sem dados = preencher manualmente</t>
+        </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="A2:I2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1173,7 +1453,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>CLIMATIZAÇÃO — DETALHAMENTO</t>
         </is>
@@ -1182,7 +1462,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total estimado (mediana de 18 similares): R$ 647.547  |  R$/m²: 39.25</t>
+          <t>Total estimado (mediana de 18 similares): R$ 765.283  |  R$/m²: 39.25</t>
         </is>
       </c>
     </row>
@@ -1229,960 +1509,960 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="A5" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>Mão de obra</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>Unid.</t>
         </is>
       </c>
-      <c r="D5" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="18" t="n">
+      <c r="D5" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="28" t="n">
         <v>190067.16456</v>
       </c>
-      <c r="F5" s="19" t="n">
+      <c r="F5" s="29" t="n">
         <v>190067.16456</v>
       </c>
-      <c r="G5" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="16" t="inlineStr">
+      <c r="G5" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="n">
+      <c r="A6" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>Cabo shieldado</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>vb</t>
         </is>
       </c>
-      <c r="D6" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="18" t="n">
+      <c r="D6" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="28" t="n">
         <v>67500</v>
       </c>
-      <c r="F6" s="19" t="n">
+      <c r="F6" s="29" t="n">
         <v>67500</v>
       </c>
-      <c r="G6" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="16" t="inlineStr">
+      <c r="G6" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="n">
+      <c r="A7" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>MINI EXAUSTOR HELICOCENTRIFUGO DE BAIXO PERFIL E BAIXO RUÍDO FABRICADO EM PLÁSTICO SILENT-300 PLUS Soler &amp; Palau (LxAxP)=214x214x149 mm 21W/220V/60Hz</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="27" t="n">
         <v>56</v>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="E7" s="28" t="n">
         <v>360.9</v>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F7" s="29" t="n">
         <v>20210.4</v>
       </c>
-      <c r="G7" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="G7" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="n">
+      <c r="A8" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>VENEZIANA DE DESCARGA DE AR COM PERFIL EM ALUMÍNIO GRA-70 SOLER &amp; PALAU 100x100</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="28" t="n">
         <v>270</v>
       </c>
-      <c r="F8" s="19" t="n">
+      <c r="F8" s="29" t="n">
         <v>1080</v>
       </c>
-      <c r="G8" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="G8" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="n">
+      <c r="A9" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="24" t="inlineStr">
         <is>
           <t>TUBULAÇÃO FRIGORÍGENA DE COBRE 3/4" PARANAPANEMA - ELUMA</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="27" t="n">
         <v>391.6</v>
       </c>
-      <c r="E9" s="18" t="n">
+      <c r="E9" s="28" t="n">
         <v>47.5</v>
       </c>
-      <c r="F9" s="19" t="n">
+      <c r="F9" s="29" t="n">
         <v>18601</v>
       </c>
-      <c r="G9" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="16" t="inlineStr">
+      <c r="G9" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="n">
+      <c r="A10" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="24" t="inlineStr">
         <is>
           <t>UNIDADE EVAPORADORA DO TIPO CASSETE MINISPLIT - 48.000 BTU/h - R410A FCQ48AVL Daikin (LxAxP)=950x500x950 mm</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="E10" s="18" t="n">
+      <c r="E10" s="28" t="n">
         <v>8847.530000000001</v>
       </c>
-      <c r="F10" s="19" t="n">
+      <c r="F10" s="29" t="n">
         <v>17695.06</v>
       </c>
-      <c r="G10" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="16" t="inlineStr">
+      <c r="G10" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="n">
+      <c r="A11" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>TUBULAÇÃO FRIGORÍGENA DE COBRE 1/2" PARANAPANEMA - ELUMA</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="27" t="n">
         <v>66.40000000000001</v>
       </c>
-      <c r="E11" s="18" t="n">
+      <c r="E11" s="28" t="n">
         <v>39.5</v>
       </c>
-      <c r="F11" s="19" t="n">
+      <c r="F11" s="29" t="n">
         <v>2622.8</v>
       </c>
-      <c r="G11" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="16" t="inlineStr">
+      <c r="G11" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="n">
+      <c r="A12" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t>Unidade Condensadora 36.000 BTU/h, LG ou similar</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>Unid.</t>
         </is>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="27" t="n">
         <v>3.5</v>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="E12" s="28" t="n">
         <v>4500</v>
       </c>
-      <c r="F12" s="19" t="n">
+      <c r="F12" s="29" t="n">
         <v>15750</v>
       </c>
-      <c r="G12" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="16" t="inlineStr">
+      <c r="G12" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="n">
+      <c r="A13" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="24" t="inlineStr">
         <is>
           <t>Unidade Evaporadora Hi wall, 36000 BTU/h, LG ou similar</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>Unid.</t>
         </is>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="27" t="n">
         <v>3.5</v>
       </c>
-      <c r="E13" s="18" t="n">
+      <c r="E13" s="28" t="n">
         <v>4252.53</v>
       </c>
-      <c r="F13" s="19" t="n">
+      <c r="F13" s="29" t="n">
         <v>14883.855</v>
       </c>
-      <c r="G13" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="16" t="inlineStr">
+      <c r="G13" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="n">
+      <c r="A14" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="24" t="inlineStr">
         <is>
           <t>Rele de Sobre Carga</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>vb</t>
         </is>
       </c>
-      <c r="D14" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E14" s="18" t="n">
+      <c r="D14" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="28" t="n">
         <v>11280</v>
       </c>
-      <c r="F14" s="19" t="n">
+      <c r="F14" s="29" t="n">
         <v>11280</v>
       </c>
-      <c r="G14" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="16" t="inlineStr">
+      <c r="G14" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="n">
+      <c r="A15" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="24" t="inlineStr">
         <is>
           <t>VENTILADOR AXIAL PARA EXAUSTÃO DE GARAGEM VHF - 4 - MOD 280 BERLINERLUFT  0,55kW/380V/3F</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D15" s="17" t="n">
+      <c r="D15" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="E15" s="18" t="n">
+      <c r="E15" s="28" t="n">
         <v>5600</v>
       </c>
-      <c r="F15" s="19" t="n">
+      <c r="F15" s="29" t="n">
         <v>11200</v>
       </c>
-      <c r="G15" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="16" t="inlineStr">
+      <c r="G15" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="n">
+      <c r="A16" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B16" s="24" t="inlineStr">
         <is>
           <t>ESPUMA ELASTOMÉTRICA PAREDE DE 13 mm 3/4"</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="D16" s="27" t="n">
         <v>391.6</v>
       </c>
-      <c r="E16" s="18" t="n">
+      <c r="E16" s="28" t="n">
         <v>22.5</v>
       </c>
-      <c r="F16" s="19" t="n">
+      <c r="F16" s="29" t="n">
         <v>8811</v>
       </c>
-      <c r="G16" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="16" t="inlineStr">
+      <c r="G16" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="n">
+      <c r="A17" s="23" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="24" t="inlineStr">
         <is>
           <t>UNIDADE EVAPORADORA DO TIPO HI-WALL SPLIT - 24000 BTU/h - SMART R-32 FTHP24Q5VL Daikin (LxAxP)=990x295x263 mm</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D17" s="27" t="n">
         <v>47</v>
       </c>
-      <c r="E17" s="18" t="n">
+      <c r="E17" s="28" t="n">
         <v>1979</v>
       </c>
-      <c r="F17" s="19" t="n">
+      <c r="F17" s="29" t="n">
         <v>93013</v>
       </c>
-      <c r="G17" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="16" t="inlineStr">
+      <c r="G17" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="n">
+      <c r="A18" s="23" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B18" s="24" t="inlineStr">
         <is>
           <t>ESPUMA ELASTOMÉTRICA PAREDE DE 13 mm 1/2"</t>
         </is>
       </c>
-      <c r="C18" s="15" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="D18" s="17" t="n">
+      <c r="D18" s="27" t="n">
         <v>66.40000000000001</v>
       </c>
-      <c r="E18" s="18" t="n">
+      <c r="E18" s="28" t="n">
         <v>17.5</v>
       </c>
-      <c r="F18" s="19" t="n">
+      <c r="F18" s="29" t="n">
         <v>1162</v>
       </c>
-      <c r="G18" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="16" t="inlineStr">
+      <c r="G18" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="n">
+      <c r="A19" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>Unidade Condensadora 24.000 BTU/h, LG ou similar</t>
         </is>
       </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>Unid.</t>
         </is>
       </c>
-      <c r="D19" s="17" t="n">
+      <c r="D19" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="E19" s="18" t="n">
+      <c r="E19" s="28" t="n">
         <v>3901.59</v>
       </c>
-      <c r="F19" s="19" t="n">
+      <c r="F19" s="29" t="n">
         <v>7803.18</v>
       </c>
-      <c r="G19" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="16" t="inlineStr">
+      <c r="G19" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="n">
+      <c r="A20" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B20" s="24" t="inlineStr">
         <is>
           <t>Rele de falta de fase</t>
         </is>
       </c>
-      <c r="C20" s="15" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>vb</t>
         </is>
       </c>
-      <c r="D20" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" s="18" t="n">
+      <c r="D20" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="28" t="n">
         <v>7050</v>
       </c>
-      <c r="F20" s="19" t="n">
+      <c r="F20" s="29" t="n">
         <v>7050</v>
       </c>
-      <c r="G20" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="16" t="inlineStr">
+      <c r="G20" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="n">
+      <c r="A21" s="23" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="24" t="inlineStr">
         <is>
           <t>UNIDADE CONDENSADORA SISTEMA MINI SPLIT COM DESCARGA DE AR HORIZONTAL PARA HIWALL-12.000 BTU/h - SMART R-32 RHP12Q5VL Daikin (LxAxP)=740x550x326 mm 951W/220V/1F</t>
         </is>
       </c>
-      <c r="C21" s="15" t="inlineStr">
+      <c r="C21" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D21" s="17" t="n">
+      <c r="D21" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="E21" s="18" t="n">
+      <c r="E21" s="28" t="n">
         <v>1699.99</v>
       </c>
-      <c r="F21" s="19" t="n">
+      <c r="F21" s="29" t="n">
         <v>6799.96</v>
       </c>
-      <c r="G21" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="16" t="inlineStr">
+      <c r="G21" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="n">
+      <c r="A22" s="23" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B22" s="24" t="inlineStr">
         <is>
           <t>Unidade Evaporadora Hi wall, 24000 BTU/h, LG ou similar</t>
         </is>
       </c>
-      <c r="C22" s="15" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>Unid.</t>
         </is>
       </c>
-      <c r="D22" s="17" t="n">
+      <c r="D22" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="E22" s="18" t="n">
+      <c r="E22" s="28" t="n">
         <v>3311.42</v>
       </c>
-      <c r="F22" s="19" t="n">
+      <c r="F22" s="29" t="n">
         <v>6622.84</v>
       </c>
-      <c r="G22" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="16" t="inlineStr">
+      <c r="G22" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="n">
+      <c r="A23" s="23" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B23" s="24" t="inlineStr">
         <is>
           <t>Unidade Condensadora Multisplit 36.000 BTU/h, LG ou similar</t>
         </is>
       </c>
-      <c r="C23" s="15" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>Unid.</t>
         </is>
       </c>
-      <c r="D23" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" s="18" t="n">
+      <c r="D23" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" s="28" t="n">
         <v>6558.35</v>
       </c>
-      <c r="F23" s="19" t="n">
+      <c r="F23" s="29" t="n">
         <v>6558.35</v>
       </c>
-      <c r="G23" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="16" t="inlineStr">
+      <c r="G23" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="n">
+      <c r="A24" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B24" s="24" t="inlineStr">
         <is>
           <t>Fusiveis de Força e Comando</t>
         </is>
       </c>
-      <c r="C24" s="15" t="inlineStr">
+      <c r="C24" s="23" t="inlineStr">
         <is>
           <t>vb</t>
         </is>
       </c>
-      <c r="D24" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" s="18" t="n">
+      <c r="D24" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="28" t="n">
         <v>6110</v>
       </c>
-      <c r="F24" s="19" t="n">
+      <c r="F24" s="29" t="n">
         <v>6110</v>
       </c>
-      <c r="G24" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" s="16" t="inlineStr">
+      <c r="G24" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="n">
+      <c r="A25" s="23" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="16" t="inlineStr">
+      <c r="B25" s="24" t="inlineStr">
         <is>
           <t>TUBULAÇÃO FRIGORÍGENA DE COBRE 3/8" PARANAPANEMA - ELUMA</t>
         </is>
       </c>
-      <c r="C25" s="15" t="inlineStr">
+      <c r="C25" s="23" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="D25" s="17" t="n">
+      <c r="D25" s="27" t="n">
         <v>87.55000000000001</v>
       </c>
-      <c r="E25" s="18" t="n">
+      <c r="E25" s="28" t="n">
         <v>26</v>
       </c>
-      <c r="F25" s="19" t="n">
+      <c r="F25" s="29" t="n">
         <v>2276.3</v>
       </c>
-      <c r="G25" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" s="16" t="inlineStr">
+      <c r="G25" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="n">
+      <c r="A26" s="23" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B26" s="24" t="inlineStr">
         <is>
           <t>Interligações Elétricas</t>
         </is>
       </c>
-      <c r="C26" s="15" t="inlineStr">
+      <c r="C26" s="23" t="inlineStr">
         <is>
           <t>vb</t>
         </is>
       </c>
-      <c r="D26" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="18" t="n">
+      <c r="D26" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="28" t="n">
         <v>5500</v>
       </c>
-      <c r="F26" s="19" t="n">
+      <c r="F26" s="29" t="n">
         <v>5500</v>
       </c>
-      <c r="G26" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="16" t="inlineStr">
+      <c r="G26" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="n">
+      <c r="A27" s="23" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="16" t="inlineStr">
+      <c r="B27" s="24" t="inlineStr">
         <is>
           <t>DUTO RETANGULAR EM AÇO GALVANIZADO 297x197 #26</t>
         </is>
       </c>
-      <c r="C27" s="15" t="inlineStr">
+      <c r="C27" s="23" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="D27" s="17" t="n">
+      <c r="D27" s="27" t="n">
         <v>25.92</v>
       </c>
-      <c r="E27" s="18" t="n">
+      <c r="E27" s="28" t="n">
         <v>192.66</v>
       </c>
-      <c r="F27" s="19" t="n">
+      <c r="F27" s="29" t="n">
         <v>4993.7472</v>
       </c>
-      <c r="G27" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="16" t="inlineStr">
+      <c r="G27" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="n">
+      <c r="A28" s="23" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="16" t="inlineStr">
+      <c r="B28" s="24" t="inlineStr">
         <is>
           <t>Unidade Condensadora 12.000 BTU/h, LG ou similar</t>
         </is>
       </c>
-      <c r="C28" s="15" t="inlineStr">
+      <c r="C28" s="23" t="inlineStr">
         <is>
           <t>Unid.</t>
         </is>
       </c>
-      <c r="D28" s="17" t="n">
+      <c r="D28" s="27" t="n">
         <v>2.5</v>
       </c>
-      <c r="E28" s="18" t="n">
+      <c r="E28" s="28" t="n">
         <v>1918.08</v>
       </c>
-      <c r="F28" s="19" t="n">
+      <c r="F28" s="29" t="n">
         <v>4795.2</v>
       </c>
-      <c r="G28" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" s="16" t="inlineStr">
+      <c r="G28" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="n">
+      <c r="A29" s="23" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="16" t="inlineStr">
+      <c r="B29" s="24" t="inlineStr">
         <is>
           <t>Chave Contatora</t>
         </is>
       </c>
-      <c r="C29" s="15" t="inlineStr">
+      <c r="C29" s="23" t="inlineStr">
         <is>
           <t>vb</t>
         </is>
       </c>
-      <c r="D29" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" s="18" t="n">
+      <c r="D29" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" s="28" t="n">
         <v>4700</v>
       </c>
-      <c r="F29" s="19" t="n">
+      <c r="F29" s="29" t="n">
         <v>4700</v>
       </c>
-      <c r="G29" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" s="16" t="inlineStr">
+      <c r="G29" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="n">
+      <c r="A30" s="23" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="16" t="inlineStr">
+      <c r="B30" s="24" t="inlineStr">
         <is>
           <t>Unidade Evaporadora Hi wall, 12000 BTU/h, LG ou similar</t>
         </is>
       </c>
-      <c r="C30" s="15" t="inlineStr">
+      <c r="C30" s="23" t="inlineStr">
         <is>
           <t>Unid.</t>
         </is>
       </c>
-      <c r="D30" s="17" t="n">
+      <c r="D30" s="27" t="n">
         <v>2.5</v>
       </c>
-      <c r="E30" s="18" t="n">
+      <c r="E30" s="28" t="n">
         <v>1792.01</v>
       </c>
-      <c r="F30" s="19" t="n">
+      <c r="F30" s="29" t="n">
         <v>4480.025</v>
       </c>
-      <c r="G30" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" s="16" t="inlineStr">
+      <c r="G30" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="n">
+      <c r="A31" s="23" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="16" t="inlineStr">
+      <c r="B31" s="24" t="inlineStr">
         <is>
           <t>Contatos Auxiliares para Interligação com Sistema de Automação</t>
         </is>
       </c>
-      <c r="C31" s="15" t="inlineStr">
+      <c r="C31" s="23" t="inlineStr">
         <is>
           <t>vb</t>
         </is>
       </c>
-      <c r="D31" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E31" s="18" t="n">
+      <c r="D31" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E31" s="28" t="n">
         <v>3760</v>
       </c>
-      <c r="F31" s="19" t="n">
+      <c r="F31" s="29" t="n">
         <v>3760</v>
       </c>
-      <c r="G31" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" s="16" t="inlineStr">
+      <c r="G31" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="n">
+      <c r="A32" s="23" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="16" t="inlineStr">
+      <c r="B32" s="24" t="inlineStr">
         <is>
           <t>VENTILADORES HELICOCENTRÍFUGOS INLINE SILENT TD-500/150 TD-500/150 SILENT Soler &amp; Palau (LxAxP)=204x252x462 mm 65W/220/1F</t>
         </is>
       </c>
-      <c r="C32" s="15" t="inlineStr">
+      <c r="C32" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D32" s="17" t="n">
+      <c r="D32" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="E32" s="18" t="n">
+      <c r="E32" s="28" t="n">
         <v>1650</v>
       </c>
-      <c r="F32" s="19" t="n">
+      <c r="F32" s="29" t="n">
         <v>3300</v>
       </c>
-      <c r="G32" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" s="16" t="inlineStr">
+      <c r="G32" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="n">
+      <c r="A33" s="23" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="16" t="inlineStr">
+      <c r="B33" s="24" t="inlineStr">
         <is>
           <t>Unidade Evaporadora Hi wall, 9000 BTU/h, LG ou similar</t>
         </is>
       </c>
-      <c r="C33" s="15" t="inlineStr">
+      <c r="C33" s="23" t="inlineStr">
         <is>
           <t>Unid.</t>
         </is>
       </c>
-      <c r="D33" s="17" t="n">
+      <c r="D33" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="E33" s="18" t="n">
+      <c r="E33" s="28" t="n">
         <v>1625</v>
       </c>
-      <c r="F33" s="19" t="n">
+      <c r="F33" s="29" t="n">
         <v>3250</v>
       </c>
-      <c r="G33" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" s="16" t="inlineStr">
+      <c r="G33" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="n">
+      <c r="A34" s="23" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="16" t="inlineStr">
+      <c r="B34" s="24" t="inlineStr">
         <is>
           <t>VENTILADORES HELICOCENTRÍFUGOS INLINE SILENT TD-1300/200 TD-1300/200 SILENT Soler &amp; Palau (LxAxC)=387x331x680mm 220W/220V/1F</t>
         </is>
       </c>
-      <c r="C34" s="15" t="inlineStr">
+      <c r="C34" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D34" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E34" s="18" t="n">
+      <c r="D34" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E34" s="28" t="n">
         <v>3200</v>
       </c>
-      <c r="F34" s="19" t="n">
+      <c r="F34" s="29" t="n">
         <v>3200</v>
       </c>
-      <c r="G34" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" s="16" t="inlineStr">
+      <c r="G34" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
@@ -2218,7 +2498,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>REV. INTERNO PAREDE — DETALHAMENTO</t>
         </is>
@@ -2227,7 +2507,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total estimado (mediana de 61 similares): R$ 1.547.726  |  R$/m²: 93.80</t>
+          <t>Total estimado (mediana de 61 similares): R$ 1.829.131  |  R$/m²: 93.80</t>
         </is>
       </c>
     </row>
@@ -2274,12 +2554,42 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
-          <t>(sem detalhamento granular nos similares — usar valor agregado acima)</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="inlineStr"/>
+      <c r="A5" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>Esquadrias (ex: Esquadrias de Alumínio - )</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="24" t="inlineStr">
+        <is>
+          <t>amalfi-tramonti</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2311,7 +2621,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>TETO — DETALHAMENTO</t>
         </is>
@@ -2320,7 +2630,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total estimado (mediana de 35 similares): R$ 1.040.660  |  R$/m²: 63.07</t>
+          <t>Total estimado (mediana de 35 similares): R$ 1.182.568  |  R$/m²: 63.07</t>
         </is>
       </c>
     </row>
@@ -2367,12 +2677,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>(sem detalhamento granular nos similares — usar valor agregado acima)</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr"/>
+      <c r="B5" s="26" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2404,7 +2714,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>PISOS — DETALHAMENTO</t>
         </is>
@@ -2413,7 +2723,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total estimado (mediana de 42 similares): R$ 3.330.979  |  R$/m²: 201.88</t>
+          <t>Total estimado (mediana de 42 similares): R$ 4.239.428  |  R$/m²: 201.88</t>
         </is>
       </c>
     </row>
@@ -2460,12 +2770,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>(sem detalhamento granular nos similares — usar valor agregado acima)</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr"/>
+      <c r="B5" s="26" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2497,7 +2807,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>PINTURA — DETALHAMENTO</t>
         </is>
@@ -2506,7 +2816,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total estimado (mediana de 61 similares): R$ 2.062.187  |  R$/m²: 124.98</t>
+          <t>Total estimado (mediana de 61 similares): R$ 2.249.658  |  R$/m²: 124.98</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2863,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>(sem detalhamento granular nos similares — usar valor agregado acima)</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr"/>
+      <c r="B5" s="26" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2590,7 +2900,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>ESQUADRIAS — DETALHAMENTO</t>
         </is>
@@ -2599,7 +2909,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total estimado (mediana de 56 similares): R$ 5.083.756  |  R$/m²: 308.11</t>
+          <t>Total estimado (mediana de 56 similares): R$ 6.470.234  |  R$/m²: 308.11</t>
         </is>
       </c>
     </row>
@@ -2646,224 +2956,224 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="A5" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>Barramento blindado (busway) ventilado 650 A – alumínio</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="27" t="n">
         <v>90</v>
       </c>
-      <c r="E5" s="18" t="n">
+      <c r="E5" s="28" t="n">
         <v>950</v>
       </c>
-      <c r="F5" s="19" t="n">
+      <c r="F5" s="29" t="n">
         <v>85500</v>
       </c>
-      <c r="G5" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="16" t="inlineStr">
+      <c r="G5" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="n">
+      <c r="A6" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>Curva horizontal (alumínio – 650A)</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="E6" s="18" t="n">
+      <c r="E6" s="28" t="n">
         <v>1950</v>
       </c>
-      <c r="F6" s="19" t="n">
+      <c r="F6" s="29" t="n">
         <v>13650</v>
       </c>
-      <c r="G6" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="16" t="inlineStr">
+      <c r="G6" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="n">
+      <c r="A7" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>Curva vertical V2020 (alumínio – 650A)</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="E7" s="28" t="n">
         <v>2100</v>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F7" s="29" t="n">
         <v>12600</v>
       </c>
-      <c r="G7" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="G7" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="n">
+      <c r="A8" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>Cabeamento MT (alumínio isolado 15kV) – 3x70mm²</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="27" t="n">
         <v>60</v>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="28" t="n">
         <v>150</v>
       </c>
-      <c r="F8" s="19" t="n">
+      <c r="F8" s="29" t="n">
         <v>9000</v>
       </c>
-      <c r="G8" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="G8" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="n">
+      <c r="A9" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="24" t="inlineStr">
         <is>
           <t>S.A.L. - Placa "Porta corta fogo - Manter fechada"</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="27" t="n">
         <v>76</v>
       </c>
-      <c r="E9" s="18" t="n">
+      <c r="E9" s="28" t="n">
         <v>49.1</v>
       </c>
-      <c r="F9" s="19" t="n">
+      <c r="F9" s="29" t="n">
         <v>3731.6</v>
       </c>
-      <c r="G9" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="16" t="inlineStr">
+      <c r="G9" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="n">
+      <c r="A10" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="24" t="inlineStr">
         <is>
           <t>Condulete de alumínio Tipo ''TB'', à prova de tempo, com tampa cega, junta de vedação em E.V.A, pintura epoxi cor cinza, para eletroduto rígido de aço DN25mm, rosca Ø1'' BSP</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="E10" s="18" t="n">
+      <c r="E10" s="28" t="n">
         <v>21.54</v>
       </c>
-      <c r="F10" s="19" t="n">
+      <c r="F10" s="29" t="n">
         <v>43.08</v>
       </c>
-      <c r="G10" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="16" t="inlineStr">
+      <c r="G10" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="n">
+      <c r="A11" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>Tampas p/ condulete alumínio e PVC</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="E11" s="18" t="n">
+      <c r="E11" s="28" t="n">
         <v>9</v>
       </c>
-      <c r="F11" s="19" t="n">
+      <c r="F11" s="29" t="n">
         <v>18</v>
       </c>
-      <c r="G11" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="16" t="inlineStr">
+      <c r="G11" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
@@ -2899,7 +3209,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>LOUÇAS E METAIS — DETALHAMENTO</t>
         </is>
@@ -2908,7 +3218,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total estimado (mediana de 21 similares): R$ 549.711  |  R$/m²: 33.32</t>
+          <t>Total estimado (mediana de 21 similares): R$ 749.606  |  R$/m²: 33.32</t>
         </is>
       </c>
     </row>
@@ -2955,960 +3265,960 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="A5" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>Banheiro - Bacia Sanitária / Caixa Acoplada</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="27" t="n">
         <v>213</v>
       </c>
-      <c r="E5" s="18" t="n">
+      <c r="E5" s="28" t="n">
         <v>952.5988</v>
       </c>
-      <c r="F5" s="19" t="n">
+      <c r="F5" s="29" t="n">
         <v>202903.5444</v>
       </c>
-      <c r="G5" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="16" t="inlineStr">
+      <c r="G5" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="n">
+      <c r="A6" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>Acabamento de Registro Comum</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="27" t="n">
         <v>585</v>
       </c>
-      <c r="E6" s="18" t="n">
+      <c r="E6" s="28" t="n">
         <v>176</v>
       </c>
-      <c r="F6" s="19" t="n">
+      <c r="F6" s="29" t="n">
         <v>102960</v>
       </c>
-      <c r="G6" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="16" t="inlineStr">
+      <c r="G6" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="n">
+      <c r="A7" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>REGISTRO MONOCOMANDO Ø3/4"</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="27" t="n">
         <v>180</v>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="E7" s="28" t="n">
         <v>359.9</v>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F7" s="29" t="n">
         <v>64781.99999999999</v>
       </c>
-      <c r="G7" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="G7" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="n">
+      <c r="A8" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>Regulador De Pressão 2º Estágio Com Registro De Fecho Rápido</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="27" t="n">
         <v>115</v>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="28" t="n">
         <v>271.89</v>
       </c>
-      <c r="F8" s="19" t="n">
+      <c r="F8" s="29" t="n">
         <v>31267.35</v>
       </c>
-      <c r="G8" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="G8" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="n">
+      <c r="A9" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="24" t="inlineStr">
         <is>
           <t>REGISTRO DE GAVETA  Ø3/4"</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="27" t="n">
         <v>225.5</v>
       </c>
-      <c r="E9" s="18" t="n">
+      <c r="E9" s="28" t="n">
         <v>39.59</v>
       </c>
-      <c r="F9" s="19" t="n">
+      <c r="F9" s="29" t="n">
         <v>8927.545</v>
       </c>
-      <c r="G9" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="16" t="inlineStr">
+      <c r="G9" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="n">
+      <c r="A10" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="24" t="inlineStr">
         <is>
           <t>Válvula reta com registro de Fecho Rápido 1/2'' BSP</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="27" t="n">
         <v>226</v>
       </c>
-      <c r="E10" s="18" t="n">
+      <c r="E10" s="28" t="n">
         <v>28.28</v>
       </c>
-      <c r="F10" s="19" t="n">
+      <c r="F10" s="29" t="n">
         <v>6391.280000000001</v>
       </c>
-      <c r="G10" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="16" t="inlineStr">
+      <c r="G10" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="n">
+      <c r="A11" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>Cuba Pia Cozinha - Lazer</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="E11" s="18" t="n">
+      <c r="E11" s="28" t="n">
         <v>1981.262</v>
       </c>
-      <c r="F11" s="19" t="n">
+      <c r="F11" s="29" t="n">
         <v>5943.786</v>
       </c>
-      <c r="G11" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="16" t="inlineStr">
+      <c r="G11" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="n">
+      <c r="A12" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t>REGISTRO DE GAVETA Ø1/2" - BRONZE</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="27" t="n">
         <v>180</v>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="E12" s="28" t="n">
         <v>29.9</v>
       </c>
-      <c r="F12" s="19" t="n">
+      <c r="F12" s="29" t="n">
         <v>5382</v>
       </c>
-      <c r="G12" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="16" t="inlineStr">
+      <c r="G12" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="n">
+      <c r="A13" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="24" t="inlineStr">
         <is>
           <t>Registro Globo Angular 2.1/2"</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="27" t="n">
         <v>35</v>
       </c>
-      <c r="E13" s="18" t="n">
+      <c r="E13" s="28" t="n">
         <v>149.9</v>
       </c>
-      <c r="F13" s="19" t="n">
+      <c r="F13" s="29" t="n">
         <v>5246.5</v>
       </c>
-      <c r="G13" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="16" t="inlineStr">
+      <c r="G13" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="n">
+      <c r="A14" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="24" t="inlineStr">
         <is>
           <t>Registro de Gaveta Industrial, Bronze - 2.1/2"</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="27" t="n">
         <v>12</v>
       </c>
-      <c r="E14" s="18" t="n">
+      <c r="E14" s="28" t="n">
         <v>433.48</v>
       </c>
-      <c r="F14" s="19" t="n">
+      <c r="F14" s="29" t="n">
         <v>5201.76</v>
       </c>
-      <c r="G14" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="16" t="inlineStr">
+      <c r="G14" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="n">
+      <c r="A15" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="24" t="inlineStr">
         <is>
           <t>Torneira misturador pia cozinha</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D15" s="17" t="n">
+      <c r="D15" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="E15" s="18" t="n">
+      <c r="E15" s="28" t="n">
         <v>1054.93</v>
       </c>
-      <c r="F15" s="19" t="n">
+      <c r="F15" s="29" t="n">
         <v>4219.72</v>
       </c>
-      <c r="G15" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="16" t="inlineStr">
+      <c r="G15" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="n">
+      <c r="A16" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B16" s="24" t="inlineStr">
         <is>
           <t>Torneira Lavatório mesa</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="D16" s="27" t="n">
         <v>9</v>
       </c>
-      <c r="E16" s="18" t="n">
+      <c r="E16" s="28" t="n">
         <v>350</v>
       </c>
-      <c r="F16" s="19" t="n">
+      <c r="F16" s="29" t="n">
         <v>3150</v>
       </c>
-      <c r="G16" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="16" t="inlineStr">
+      <c r="G16" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="n">
+      <c r="A17" s="23" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="24" t="inlineStr">
         <is>
           <t>REGISTRO DE GAVETA  2 1/2"</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D17" s="17" t="n">
+      <c r="D17" s="27" t="n">
         <v>7.5</v>
       </c>
-      <c r="E17" s="18" t="n">
+      <c r="E17" s="28" t="n">
         <v>350.91</v>
       </c>
-      <c r="F17" s="19" t="n">
+      <c r="F17" s="29" t="n">
         <v>2631.825</v>
       </c>
-      <c r="G17" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="16" t="inlineStr">
+      <c r="G17" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="n">
+      <c r="A18" s="23" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B18" s="24" t="inlineStr">
         <is>
           <t>SHP - Bacia de contenção - 375 Litros - Abaixo do Tanque</t>
         </is>
       </c>
-      <c r="C18" s="15" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D18" s="17" t="n">
+      <c r="D18" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="E18" s="18" t="n">
+      <c r="E18" s="28" t="n">
         <v>1259</v>
       </c>
-      <c r="F18" s="19" t="n">
+      <c r="F18" s="29" t="n">
         <v>2518</v>
       </c>
-      <c r="G18" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="16" t="inlineStr">
+      <c r="G18" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="n">
+      <c r="A19" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>Banheiro - Bacia Sanitária PNE</t>
         </is>
       </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D19" s="17" t="n">
+      <c r="D19" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="E19" s="18" t="n">
+      <c r="E19" s="28" t="n">
         <v>1166.57</v>
       </c>
-      <c r="F19" s="19" t="n">
+      <c r="F19" s="29" t="n">
         <v>2333.14</v>
       </c>
-      <c r="G19" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="16" t="inlineStr">
+      <c r="G19" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="n">
+      <c r="A20" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B20" s="24" t="inlineStr">
         <is>
           <t>GÁS - Registro de fecho rápido com caixa</t>
         </is>
       </c>
-      <c r="C20" s="15" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D20" s="17" t="n">
+      <c r="D20" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="E20" s="18" t="n">
+      <c r="E20" s="28" t="n">
         <v>1098.98</v>
       </c>
-      <c r="F20" s="19" t="n">
+      <c r="F20" s="29" t="n">
         <v>2197.96</v>
       </c>
-      <c r="G20" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="16" t="inlineStr">
+      <c r="G20" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="n">
+      <c r="A21" s="23" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="24" t="inlineStr">
         <is>
           <t>REGISTRO DE GAVETA  Ø2 1/2"</t>
         </is>
       </c>
-      <c r="C21" s="15" t="inlineStr">
+      <c r="C21" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D21" s="17" t="n">
+      <c r="D21" s="27" t="n">
         <v>6</v>
       </c>
-      <c r="E21" s="18" t="n">
+      <c r="E21" s="28" t="n">
         <v>350.91</v>
       </c>
-      <c r="F21" s="19" t="n">
+      <c r="F21" s="29" t="n">
         <v>2105.46</v>
       </c>
-      <c r="G21" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="16" t="inlineStr">
+      <c r="G21" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="n">
+      <c r="A22" s="23" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B22" s="24" t="inlineStr">
         <is>
           <t>REGISTRO DE GAVETA Ø3"</t>
         </is>
       </c>
-      <c r="C22" s="15" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D22" s="17" t="n">
+      <c r="D22" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="E22" s="18" t="n">
+      <c r="E22" s="28" t="n">
         <v>434.38</v>
       </c>
-      <c r="F22" s="19" t="n">
+      <c r="F22" s="29" t="n">
         <v>1737.52</v>
       </c>
-      <c r="G22" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="16" t="inlineStr">
+      <c r="G22" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="n">
+      <c r="A23" s="23" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B23" s="24" t="inlineStr">
         <is>
           <t>REGISTRO DE GAVETA Ø2.1/2" - BRONZE</t>
         </is>
       </c>
-      <c r="C23" s="15" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D23" s="17" t="n">
+      <c r="D23" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="E23" s="18" t="n">
+      <c r="E23" s="28" t="n">
         <v>350.91</v>
       </c>
-      <c r="F23" s="19" t="n">
+      <c r="F23" s="29" t="n">
         <v>1403.64</v>
       </c>
-      <c r="G23" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="16" t="inlineStr">
+      <c r="G23" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="n">
+      <c r="A24" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B24" s="24" t="inlineStr">
         <is>
           <t>Torneira de Jardins</t>
         </is>
       </c>
-      <c r="C24" s="15" t="inlineStr">
+      <c r="C24" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D24" s="17" t="n">
+      <c r="D24" s="27" t="n">
         <v>19</v>
       </c>
-      <c r="E24" s="18" t="n">
+      <c r="E24" s="28" t="n">
         <v>72</v>
       </c>
-      <c r="F24" s="19" t="n">
+      <c r="F24" s="29" t="n">
         <v>1368</v>
       </c>
-      <c r="G24" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" s="16" t="inlineStr">
+      <c r="G24" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="n">
+      <c r="A25" s="23" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="16" t="inlineStr">
+      <c r="B25" s="24" t="inlineStr">
         <is>
           <t>REGISTRO DE GAVETA  Ø3"</t>
         </is>
       </c>
-      <c r="C25" s="15" t="inlineStr">
+      <c r="C25" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D25" s="17" t="n">
+      <c r="D25" s="27" t="n">
         <v>3</v>
       </c>
-      <c r="E25" s="18" t="n">
+      <c r="E25" s="28" t="n">
         <v>434.38</v>
       </c>
-      <c r="F25" s="19" t="n">
+      <c r="F25" s="29" t="n">
         <v>1303.14</v>
       </c>
-      <c r="G25" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" s="16" t="inlineStr">
+      <c r="G25" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="n">
+      <c r="A26" s="23" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B26" s="24" t="inlineStr">
         <is>
           <t>REGISTRO DE GAVETA Ø2" - BRONZE</t>
         </is>
       </c>
-      <c r="C26" s="15" t="inlineStr">
+      <c r="C26" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D26" s="17" t="n">
+      <c r="D26" s="27" t="n">
         <v>5</v>
       </c>
-      <c r="E26" s="18" t="n">
+      <c r="E26" s="28" t="n">
         <v>201.6</v>
       </c>
-      <c r="F26" s="19" t="n">
+      <c r="F26" s="29" t="n">
         <v>1008</v>
       </c>
-      <c r="G26" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="16" t="inlineStr">
+      <c r="G26" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="n">
+      <c r="A27" s="23" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="16" t="inlineStr">
+      <c r="B27" s="24" t="inlineStr">
         <is>
           <t>Banheiro - Cuba de Sobrepor - PNE</t>
         </is>
       </c>
-      <c r="C27" s="15" t="inlineStr">
+      <c r="C27" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D27" s="17" t="n">
+      <c r="D27" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="E27" s="18" t="n">
+      <c r="E27" s="28" t="n">
         <v>492.8899999999999</v>
       </c>
-      <c r="F27" s="19" t="n">
+      <c r="F27" s="29" t="n">
         <v>985.7799999999999</v>
       </c>
-      <c r="G27" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="16" t="inlineStr">
+      <c r="G27" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="n">
+      <c r="A28" s="23" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="16" t="inlineStr">
+      <c r="B28" s="24" t="inlineStr">
         <is>
           <t>Cozinha - Cuba / Inox</t>
         </is>
       </c>
-      <c r="C28" s="15" t="inlineStr">
+      <c r="C28" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D28" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" s="18" t="n">
+      <c r="D28" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="28" t="n">
         <v>809.2620000000001</v>
       </c>
-      <c r="F28" s="19" t="n">
+      <c r="F28" s="29" t="n">
         <v>809.2620000000001</v>
       </c>
-      <c r="G28" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" s="16" t="inlineStr">
+      <c r="G28" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="n">
+      <c r="A29" s="23" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="16" t="inlineStr">
+      <c r="B29" s="24" t="inlineStr">
         <is>
           <t>Acabamento de Registro Pressão</t>
         </is>
       </c>
-      <c r="C29" s="15" t="inlineStr">
+      <c r="C29" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D29" s="17" t="n">
+      <c r="D29" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="E29" s="18" t="n">
+      <c r="E29" s="28" t="n">
         <v>240</v>
       </c>
-      <c r="F29" s="19" t="n">
+      <c r="F29" s="29" t="n">
         <v>480</v>
       </c>
-      <c r="G29" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" s="16" t="inlineStr">
+      <c r="G29" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="n">
+      <c r="A30" s="23" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="16" t="inlineStr">
+      <c r="B30" s="24" t="inlineStr">
         <is>
           <t>REGISTRO DE ESFERA SOLDÁVEL Ø50</t>
         </is>
       </c>
-      <c r="C30" s="15" t="inlineStr">
+      <c r="C30" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D30" s="17" t="n">
+      <c r="D30" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="E30" s="18" t="n">
+      <c r="E30" s="28" t="n">
         <v>40.9</v>
       </c>
-      <c r="F30" s="19" t="n">
+      <c r="F30" s="29" t="n">
         <v>327.2</v>
       </c>
-      <c r="G30" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" s="16" t="inlineStr">
+      <c r="G30" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="n">
+      <c r="A31" s="23" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="16" t="inlineStr">
+      <c r="B31" s="24" t="inlineStr">
         <is>
           <t>REGISTRO DE GAVETA  Ø1"</t>
         </is>
       </c>
-      <c r="C31" s="15" t="inlineStr">
+      <c r="C31" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D31" s="17" t="n">
+      <c r="D31" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="E31" s="18" t="n">
+      <c r="E31" s="28" t="n">
         <v>74.90000000000001</v>
       </c>
-      <c r="F31" s="19" t="n">
+      <c r="F31" s="29" t="n">
         <v>299.6</v>
       </c>
-      <c r="G31" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" s="16" t="inlineStr">
+      <c r="G31" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="n">
+      <c r="A32" s="23" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="16" t="inlineStr">
+      <c r="B32" s="24" t="inlineStr">
         <is>
           <t>REGISTRO GLOBO ANGULAR 45º: 2.1/2"</t>
         </is>
       </c>
-      <c r="C32" s="15" t="inlineStr">
+      <c r="C32" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D32" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" s="18" t="n">
+      <c r="D32" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="28" t="n">
         <v>140.41</v>
       </c>
-      <c r="F32" s="19" t="n">
+      <c r="F32" s="29" t="n">
         <v>140.41</v>
       </c>
-      <c r="G32" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" s="16" t="inlineStr">
+      <c r="G32" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="n">
+      <c r="A33" s="23" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="16" t="inlineStr">
+      <c r="B33" s="24" t="inlineStr">
         <is>
           <t>Válvula reta com registro de Fecho Rápido 3/4'' BSP</t>
         </is>
       </c>
-      <c r="C33" s="15" t="inlineStr">
+      <c r="C33" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D33" s="17" t="n">
+      <c r="D33" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="E33" s="18" t="n">
+      <c r="E33" s="28" t="n">
         <v>47.4</v>
       </c>
-      <c r="F33" s="19" t="n">
+      <c r="F33" s="29" t="n">
         <v>94.8</v>
       </c>
-      <c r="G33" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" s="16" t="inlineStr">
+      <c r="G33" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="n">
+      <c r="A34" s="23" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="16" t="inlineStr">
+      <c r="B34" s="24" t="inlineStr">
         <is>
           <t>REGISTRO DE GAVETA  Ø1/2"</t>
         </is>
       </c>
-      <c r="C34" s="15" t="inlineStr">
+      <c r="C34" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D34" s="17" t="n">
+      <c r="D34" s="27" t="n">
         <v>2.5</v>
       </c>
-      <c r="E34" s="18" t="n">
+      <c r="E34" s="28" t="n">
         <v>29.9</v>
       </c>
-      <c r="F34" s="19" t="n">
+      <c r="F34" s="29" t="n">
         <v>74.75</v>
       </c>
-      <c r="G34" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" s="16" t="inlineStr">
+      <c r="G34" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
@@ -3944,7 +4254,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>FACHADA — DETALHAMENTO</t>
         </is>
@@ -3953,7 +4263,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total estimado (mediana de 33 similares): R$ 2.218.818  |  R$/m²: 134.47</t>
+          <t>Total estimado (mediana de 33 similares): R$ 2.723.094  |  R$/m²: 134.47</t>
         </is>
       </c>
     </row>
@@ -4000,12 +4310,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>(sem detalhamento granular nos similares — usar valor agregado acima)</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr"/>
+      <c r="B5" s="26" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -4037,7 +4347,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>COMPLEMENTARES — DETALHAMENTO</t>
         </is>
@@ -4046,7 +4356,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total estimado (mediana de 57 similares): R$ 2.883.773  |  R$/m²: 174.77</t>
+          <t>Total estimado (mediana de 57 similares): R$ 3.145.934  |  R$/m²: 174.77</t>
         </is>
       </c>
     </row>
@@ -4093,840 +4403,840 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="A5" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>Quadra Poliesportiva</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr"/>
-      <c r="D5" s="17" t="n">
+      <c r="C5" s="23" t="inlineStr"/>
+      <c r="D5" s="27" t="n">
         <v>121.995</v>
       </c>
-      <c r="E5" s="18" t="n">
+      <c r="E5" s="28" t="n">
         <v>1168.3515625</v>
       </c>
-      <c r="F5" s="19" t="n">
+      <c r="F5" s="29" t="n">
         <v>142533.0488671875</v>
       </c>
-      <c r="G5" s="15" t="n">
+      <c r="G5" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="H5" s="16" t="inlineStr">
+      <c r="H5" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti, viva4-barra4</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="n">
+      <c r="A6" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>Banqueta Duda</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr"/>
-      <c r="D6" s="17" t="n">
+      <c r="C6" s="23" t="inlineStr"/>
+      <c r="D6" s="27" t="n">
         <v>16</v>
       </c>
-      <c r="E6" s="18" t="n">
+      <c r="E6" s="28" t="n">
         <v>5800</v>
       </c>
-      <c r="F6" s="19" t="n">
+      <c r="F6" s="29" t="n">
         <v>92800</v>
       </c>
-      <c r="G6" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="16" t="inlineStr">
+      <c r="G6" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="24" t="inlineStr">
         <is>
           <t>wf-aquarius</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="n">
+      <c r="A7" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>ESTAÇÃO DE MUSCULAÇÃO ATHLETIC POWER PLUS</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr"/>
-      <c r="D7" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="18" t="n">
+      <c r="C7" s="23" t="inlineStr"/>
+      <c r="D7" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="28" t="n">
         <v>62000</v>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F7" s="29" t="n">
         <v>62000</v>
       </c>
-      <c r="G7" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="G7" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="24" t="inlineStr">
         <is>
           <t>wf-aquarius</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="n">
+      <c r="A8" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>Cadeira Alicia Seiva Móveis</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr"/>
-      <c r="D8" s="17" t="n">
+      <c r="C8" s="23" t="inlineStr"/>
+      <c r="D8" s="27" t="n">
         <v>47</v>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="28" t="n">
         <v>1158</v>
       </c>
-      <c r="F8" s="19" t="n">
+      <c r="F8" s="29" t="n">
         <v>54426</v>
       </c>
-      <c r="G8" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="G8" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="n">
+      <c r="A9" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="24" t="inlineStr">
         <is>
           <t>Espreguiçadeira Calhetas em Corda Pet Cinza</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr"/>
-      <c r="D9" s="17" t="n">
+      <c r="C9" s="23" t="inlineStr"/>
+      <c r="D9" s="27" t="n">
         <v>8</v>
       </c>
-      <c r="E9" s="18" t="n">
+      <c r="E9" s="28" t="n">
         <v>6620</v>
       </c>
-      <c r="F9" s="19" t="n">
+      <c r="F9" s="29" t="n">
         <v>52960</v>
       </c>
-      <c r="G9" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="16" t="inlineStr">
+      <c r="G9" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="n">
+      <c r="A10" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="24" t="inlineStr">
         <is>
           <t>Esteira Profissional Adidas T-23 (T-23) - Adidas</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr"/>
-      <c r="D10" s="17" t="n">
+      <c r="C10" s="23" t="inlineStr"/>
+      <c r="D10" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="E10" s="18" t="n">
+      <c r="E10" s="28" t="n">
         <v>22654.8</v>
       </c>
-      <c r="F10" s="19" t="n">
+      <c r="F10" s="29" t="n">
         <v>45309.6</v>
       </c>
-      <c r="G10" s="15" t="n">
+      <c r="G10" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="H10" s="16" t="inlineStr">
+      <c r="H10" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti, viva4-barra4</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="n">
+      <c r="A11" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>Área:</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr"/>
-      <c r="D11" s="17" t="n">
+      <c r="C11" s="23" t="inlineStr"/>
+      <c r="D11" s="27" t="n">
         <v>42.935</v>
       </c>
-      <c r="E11" s="18" t="n">
+      <c r="E11" s="28" t="n">
         <v>1517.172284644195</v>
       </c>
-      <c r="F11" s="19" t="n">
+      <c r="F11" s="29" t="n">
         <v>65139.79204119851</v>
       </c>
-      <c r="G11" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="16" t="inlineStr">
+      <c r="G11" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="24" t="inlineStr">
         <is>
           <t>wf-aquarius</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="n">
+      <c r="A12" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t>Circuito playground</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr"/>
-      <c r="D12" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="18" t="n">
+      <c r="C12" s="23" t="inlineStr"/>
+      <c r="D12" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" s="28" t="n">
         <v>42000</v>
       </c>
-      <c r="F12" s="19" t="n">
+      <c r="F12" s="29" t="n">
         <v>42000</v>
       </c>
-      <c r="G12" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="16" t="inlineStr">
+      <c r="G12" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="24" t="inlineStr">
         <is>
           <t>wf-aquarius</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="n">
+      <c r="A13" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="24" t="inlineStr">
         <is>
           <t>Espelhos</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr"/>
-      <c r="D13" s="17" t="n">
+      <c r="C13" s="23" t="inlineStr"/>
+      <c r="D13" s="27" t="n">
         <v>2.5</v>
       </c>
-      <c r="E13" s="18" t="n">
+      <c r="E13" s="28" t="n">
         <v>40288.93390624999</v>
       </c>
-      <c r="F13" s="19" t="n">
+      <c r="F13" s="29" t="n">
         <v>100722.334765625</v>
       </c>
-      <c r="G13" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="16" t="inlineStr">
+      <c r="G13" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="24" t="inlineStr">
         <is>
           <t>viva4-barra4</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="n">
+      <c r="A14" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="24" t="inlineStr">
         <is>
           <t>Esteira Profissional Adidas T-23  (T-23) - Adidas</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr"/>
-      <c r="D14" s="17" t="n">
+      <c r="C14" s="23" t="inlineStr"/>
+      <c r="D14" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="E14" s="18" t="n">
+      <c r="E14" s="28" t="n">
         <v>20137.6</v>
       </c>
-      <c r="F14" s="19" t="n">
+      <c r="F14" s="29" t="n">
         <v>40275.2</v>
       </c>
-      <c r="G14" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="16" t="inlineStr">
+      <c r="G14" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="n">
+      <c r="A15" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="24" t="inlineStr">
         <is>
           <t>Mesa De Jantar Oval Cambridge (6 Lugares)</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr"/>
-      <c r="D15" s="17" t="n">
+      <c r="C15" s="23" t="inlineStr"/>
+      <c r="D15" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="E15" s="18" t="n">
+      <c r="E15" s="28" t="n">
         <v>8249.959999999999</v>
       </c>
-      <c r="F15" s="19" t="n">
+      <c r="F15" s="29" t="n">
         <v>32999.84</v>
       </c>
-      <c r="G15" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="16" t="inlineStr">
+      <c r="G15" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="n">
+      <c r="A16" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B16" s="24" t="inlineStr">
         <is>
           <t>Playground Dolphin Playground T em Madeira para Quintal com Escorregador</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr"/>
-      <c r="D16" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="18" t="n">
+      <c r="C16" s="23" t="inlineStr"/>
+      <c r="D16" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" s="28" t="n">
         <v>32000</v>
       </c>
-      <c r="F16" s="19" t="n">
+      <c r="F16" s="29" t="n">
         <v>32000</v>
       </c>
-      <c r="G16" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="16" t="inlineStr">
+      <c r="G16" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="n">
+      <c r="A17" s="23" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="24" t="inlineStr">
         <is>
           <t>Cadeira Arco Encosto Estofado</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr"/>
-      <c r="D17" s="17" t="n">
+      <c r="C17" s="23" t="inlineStr"/>
+      <c r="D17" s="27" t="n">
         <v>16.5</v>
       </c>
-      <c r="E17" s="18" t="n">
+      <c r="E17" s="28" t="n">
         <v>1938.9</v>
       </c>
-      <c r="F17" s="19" t="n">
+      <c r="F17" s="29" t="n">
         <v>31991.85</v>
       </c>
-      <c r="G17" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="16" t="inlineStr">
+      <c r="G17" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="n">
+      <c r="A18" s="23" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B18" s="24" t="inlineStr">
         <is>
           <t>Espreguiçadeira Alumínio Em Corda Náutica Piscina</t>
         </is>
       </c>
-      <c r="C18" s="15" t="inlineStr"/>
-      <c r="D18" s="17" t="n">
+      <c r="C18" s="23" t="inlineStr"/>
+      <c r="D18" s="27" t="n">
         <v>10.5</v>
       </c>
-      <c r="E18" s="18" t="n">
+      <c r="E18" s="28" t="n">
         <v>3100</v>
       </c>
-      <c r="F18" s="19" t="n">
+      <c r="F18" s="29" t="n">
         <v>32550</v>
       </c>
-      <c r="G18" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="16" t="inlineStr">
+      <c r="G18" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="24" t="inlineStr">
         <is>
           <t>wf-aquarius</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="n">
+      <c r="A19" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>Mêsa de sinuca</t>
         </is>
       </c>
-      <c r="C19" s="15" t="inlineStr"/>
-      <c r="D19" s="17" t="n">
+      <c r="C19" s="23" t="inlineStr"/>
+      <c r="D19" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="E19" s="18" t="n">
+      <c r="E19" s="28" t="n">
         <v>15000</v>
       </c>
-      <c r="F19" s="19" t="n">
+      <c r="F19" s="29" t="n">
         <v>30000</v>
       </c>
-      <c r="G19" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="16" t="inlineStr">
+      <c r="G19" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="24" t="inlineStr">
         <is>
           <t>wf-aquarius</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="n">
+      <c r="A20" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B20" s="24" t="inlineStr">
         <is>
           <t>Cadeira Elevador De Acessibilidade Para Piscina Everest Maro Marol</t>
         </is>
       </c>
-      <c r="C20" s="15" t="inlineStr"/>
-      <c r="D20" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" s="18" t="n">
+      <c r="C20" s="23" t="inlineStr"/>
+      <c r="D20" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="28" t="n">
         <v>29650</v>
       </c>
-      <c r="F20" s="19" t="n">
+      <c r="F20" s="29" t="n">
         <v>29650</v>
       </c>
-      <c r="G20" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="16" t="inlineStr">
+      <c r="G20" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="24" t="inlineStr">
         <is>
           <t>viva4-barra4</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="n">
+      <c r="A21" s="23" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="24" t="inlineStr">
         <is>
           <t>LG Lava e Seca Torre WashTower 14kg Black Inox</t>
         </is>
       </c>
-      <c r="C21" s="15" t="inlineStr"/>
-      <c r="D21" s="17" t="n">
+      <c r="C21" s="23" t="inlineStr"/>
+      <c r="D21" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="E21" s="18" t="n">
+      <c r="E21" s="28" t="n">
         <v>14500</v>
       </c>
-      <c r="F21" s="19" t="n">
+      <c r="F21" s="29" t="n">
         <v>29000</v>
       </c>
-      <c r="G21" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="16" t="inlineStr">
+      <c r="G21" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="n">
+      <c r="A22" s="23" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B22" s="24" t="inlineStr">
         <is>
           <t>Elíptico Adidas X-21</t>
         </is>
       </c>
-      <c r="C22" s="15" t="inlineStr"/>
-      <c r="D22" s="17" t="n">
+      <c r="C22" s="23" t="inlineStr"/>
+      <c r="D22" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="E22" s="18" t="n">
+      <c r="E22" s="28" t="n">
         <v>14490</v>
       </c>
-      <c r="F22" s="19" t="n">
+      <c r="F22" s="29" t="n">
         <v>28980</v>
       </c>
-      <c r="G22" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="16" t="inlineStr">
+      <c r="G22" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="n">
+      <c r="A23" s="23" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B23" s="24" t="inlineStr">
         <is>
           <t>Cadeira Paloma sem braçoNomade Home</t>
         </is>
       </c>
-      <c r="C23" s="15" t="inlineStr"/>
-      <c r="D23" s="17" t="n">
+      <c r="C23" s="23" t="inlineStr"/>
+      <c r="D23" s="27" t="n">
         <v>20</v>
       </c>
-      <c r="E23" s="18" t="n">
+      <c r="E23" s="28" t="n">
         <v>1390</v>
       </c>
-      <c r="F23" s="19" t="n">
+      <c r="F23" s="29" t="n">
         <v>27800</v>
       </c>
-      <c r="G23" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="16" t="inlineStr">
+      <c r="G23" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="24" t="inlineStr">
         <is>
           <t>viva4-barra4</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="n">
+      <c r="A24" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B24" s="24" t="inlineStr">
         <is>
           <t>Refrigerador Expositor Venax EXPVBL 330 Preto Fosco</t>
         </is>
       </c>
-      <c r="C24" s="15" t="inlineStr"/>
-      <c r="D24" s="17" t="n">
+      <c r="C24" s="23" t="inlineStr"/>
+      <c r="D24" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="E24" s="18" t="n">
+      <c r="E24" s="28" t="n">
         <v>6890</v>
       </c>
-      <c r="F24" s="19" t="n">
+      <c r="F24" s="29" t="n">
         <v>27560</v>
       </c>
-      <c r="G24" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" s="16" t="inlineStr">
+      <c r="G24" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="n">
+      <c r="A25" s="23" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="16" t="inlineStr">
+      <c r="B25" s="24" t="inlineStr">
         <is>
           <t>Espreguiçadeira Aste</t>
         </is>
       </c>
-      <c r="C25" s="15" t="inlineStr"/>
-      <c r="D25" s="17" t="n">
+      <c r="C25" s="23" t="inlineStr"/>
+      <c r="D25" s="27" t="n">
         <v>4.5</v>
       </c>
-      <c r="E25" s="18" t="n">
+      <c r="E25" s="28" t="n">
         <v>5589.14</v>
       </c>
-      <c r="F25" s="19" t="n">
+      <c r="F25" s="29" t="n">
         <v>25151.13</v>
       </c>
-      <c r="G25" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" s="16" t="inlineStr">
+      <c r="G25" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="n">
+      <c r="A26" s="23" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B26" s="24" t="inlineStr">
         <is>
           <t>Mesa de Bilhar Versátil 2P Vintage</t>
         </is>
       </c>
-      <c r="C26" s="15" t="inlineStr"/>
-      <c r="D26" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="18" t="n">
+      <c r="C26" s="23" t="inlineStr"/>
+      <c r="D26" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="28" t="n">
         <v>24000</v>
       </c>
-      <c r="F26" s="19" t="n">
+      <c r="F26" s="29" t="n">
         <v>24000</v>
       </c>
-      <c r="G26" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="16" t="inlineStr">
+      <c r="G26" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="24" t="inlineStr">
         <is>
           <t>viva4-barra4</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="n">
+      <c r="A27" s="23" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="16" t="inlineStr">
+      <c r="B27" s="24" t="inlineStr">
         <is>
           <t>Mesa De Jantar Oval Cambridge (4 Lugares)</t>
         </is>
       </c>
-      <c r="C27" s="15" t="inlineStr"/>
-      <c r="D27" s="17" t="n">
+      <c r="C27" s="23" t="inlineStr"/>
+      <c r="D27" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="E27" s="18" t="n">
+      <c r="E27" s="28" t="n">
         <v>5483.96</v>
       </c>
-      <c r="F27" s="19" t="n">
+      <c r="F27" s="29" t="n">
         <v>21935.84</v>
       </c>
-      <c r="G27" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="16" t="inlineStr">
+      <c r="G27" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="n">
+      <c r="A28" s="23" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="16" t="inlineStr">
+      <c r="B28" s="24" t="inlineStr">
         <is>
           <t>Hyper Cross com Smith Vibranium - 60 kg  (VHC-60) - VIBRANIUM</t>
         </is>
       </c>
-      <c r="C28" s="15" t="inlineStr"/>
-      <c r="D28" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" s="18" t="n">
+      <c r="C28" s="23" t="inlineStr"/>
+      <c r="D28" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" s="28" t="n">
         <v>20720</v>
       </c>
-      <c r="F28" s="19" t="n">
+      <c r="F28" s="29" t="n">
         <v>20720</v>
       </c>
-      <c r="G28" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" s="16" t="inlineStr">
+      <c r="G28" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="n">
+      <c r="A29" s="23" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="16" t="inlineStr">
+      <c r="B29" s="24" t="inlineStr">
         <is>
           <t>Mêsa de poker</t>
         </is>
       </c>
-      <c r="C29" s="15" t="inlineStr"/>
-      <c r="D29" s="17" t="n">
+      <c r="C29" s="23" t="inlineStr"/>
+      <c r="D29" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="E29" s="18" t="n">
+      <c r="E29" s="28" t="n">
         <v>10000</v>
       </c>
-      <c r="F29" s="19" t="n">
+      <c r="F29" s="29" t="n">
         <v>20000</v>
       </c>
-      <c r="G29" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" s="16" t="inlineStr">
+      <c r="G29" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="24" t="inlineStr">
         <is>
           <t>wf-aquarius</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="n">
+      <c r="A30" s="23" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="16" t="inlineStr">
+      <c r="B30" s="24" t="inlineStr">
         <is>
           <t>Mesa bistro horizon</t>
         </is>
       </c>
-      <c r="C30" s="15" t="inlineStr"/>
-      <c r="D30" s="17" t="n">
+      <c r="C30" s="23" t="inlineStr"/>
+      <c r="D30" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="E30" s="18" t="n">
+      <c r="E30" s="28" t="n">
         <v>4999</v>
       </c>
-      <c r="F30" s="19" t="n">
+      <c r="F30" s="29" t="n">
         <v>19996</v>
       </c>
-      <c r="G30" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" s="16" t="inlineStr">
+      <c r="G30" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="n">
+      <c r="A31" s="23" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="16" t="inlineStr">
+      <c r="B31" s="24" t="inlineStr">
         <is>
           <t>Poltronas</t>
         </is>
       </c>
-      <c r="C31" s="15" t="inlineStr"/>
-      <c r="D31" s="17" t="n">
+      <c r="C31" s="23" t="inlineStr"/>
+      <c r="D31" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="E31" s="18" t="n">
+      <c r="E31" s="28" t="n">
         <v>9990</v>
       </c>
-      <c r="F31" s="19" t="n">
+      <c r="F31" s="29" t="n">
         <v>19980</v>
       </c>
-      <c r="G31" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" s="16" t="inlineStr">
+      <c r="G31" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="24" t="inlineStr">
         <is>
           <t>wf-aquarius</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="n">
+      <c r="A32" s="23" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="16" t="inlineStr">
+      <c r="B32" s="24" t="inlineStr">
         <is>
           <t>Sofá sun braço esquerdo</t>
         </is>
       </c>
-      <c r="C32" s="15" t="inlineStr"/>
-      <c r="D32" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" s="18" t="n">
+      <c r="C32" s="23" t="inlineStr"/>
+      <c r="D32" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="28" t="n">
         <v>19499</v>
       </c>
-      <c r="F32" s="19" t="n">
+      <c r="F32" s="29" t="n">
         <v>19499</v>
       </c>
-      <c r="G32" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" s="16" t="inlineStr">
+      <c r="G32" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="n">
+      <c r="A33" s="23" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="16" t="inlineStr">
+      <c r="B33" s="24" t="inlineStr">
         <is>
           <t>Cadeira Com Almofada Em Corda Náutica Área Externa</t>
         </is>
       </c>
-      <c r="C33" s="15" t="inlineStr"/>
-      <c r="D33" s="17" t="n">
+      <c r="C33" s="23" t="inlineStr"/>
+      <c r="D33" s="27" t="n">
         <v>24</v>
       </c>
-      <c r="E33" s="18" t="n">
+      <c r="E33" s="28" t="n">
         <v>811.2</v>
       </c>
-      <c r="F33" s="19" t="n">
+      <c r="F33" s="29" t="n">
         <v>19468.8</v>
       </c>
-      <c r="G33" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" s="16" t="inlineStr">
+      <c r="G33" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="24" t="inlineStr">
         <is>
           <t>viva4-barra4</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="n">
+      <c r="A34" s="23" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="16" t="inlineStr">
+      <c r="B34" s="24" t="inlineStr">
         <is>
           <t>Cadeira Palermo Scaburi</t>
         </is>
       </c>
-      <c r="C34" s="15" t="inlineStr"/>
-      <c r="D34" s="17" t="n">
+      <c r="C34" s="23" t="inlineStr"/>
+      <c r="D34" s="27" t="n">
         <v>7.5</v>
       </c>
-      <c r="E34" s="18" t="n">
+      <c r="E34" s="28" t="n">
         <v>2530</v>
       </c>
-      <c r="F34" s="19" t="n">
+      <c r="F34" s="29" t="n">
         <v>18975</v>
       </c>
-      <c r="G34" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" s="16" t="inlineStr">
+      <c r="G34" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="24" t="inlineStr">
         <is>
           <t>viva4-barra4</t>
         </is>
@@ -4962,7 +5272,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>IMPREVISTOS — DETALHAMENTO</t>
         </is>
@@ -4971,7 +5281,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total estimado (mediana de 23 similares): R$ 839.616  |  R$/m²: 50.89</t>
+          <t>Total estimado (mediana de 23 similares): R$ 763.287  |  R$/m²: 50.89</t>
         </is>
       </c>
     </row>
@@ -5018,12 +5328,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>(sem detalhamento granular nos similares — usar valor agregado acima)</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr"/>
+      <c r="B5" s="26" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5041,7 +5351,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5055,7 +5365,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>GERENCIAMENTO — DETALHAMENTO</t>
         </is>
@@ -5111,12 +5421,118 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
-          <t>(sem detalhamento granular nos similares — usar valor agregado acima)</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="inlineStr"/>
+      <c r="A5" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
+        <is>
+          <t>Locação de Equipamentos (ex: Locação de balancim elétr | Locação de grua)</t>
+        </is>
+      </c>
+      <c r="C5" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="H5" s="24" t="inlineStr">
+        <is>
+          <t>fonseca-empreendimentos-estoril, xpcon-porto-cerro</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>Mão de Obra e Equipe (ex: Rateio equipe administrat | Engenheiro civil)</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D6" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="24" t="inlineStr">
+        <is>
+          <t>fonseca-empreendimentos-estoril</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>Documentação Legal e Projetos (ex: Projeto Arquitetônico Leg | Projeto estrutural)</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="24" t="inlineStr">
+        <is>
+          <t>viva4-barra4</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5146,7 +5562,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>PROJETOS DE REFERÊNCIA usados na geração automatizada</t>
         </is>
@@ -5185,106 +5601,106 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="A4" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="18" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
-      <c r="C4" s="25" t="n">
+      <c r="C4" s="37" t="n">
         <v>15602.85</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="36" t="n">
         <v>90</v>
       </c>
-      <c r="E4" s="7" t="n">
+      <c r="E4" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="6" t="n"/>
+      <c r="F4" s="39" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="n">
+      <c r="A5" s="36" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="18" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
-      <c r="C5" s="25" t="n">
+      <c r="C5" s="37" t="n">
         <v>14491.98</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="36" t="n">
         <v>110</v>
       </c>
-      <c r="E5" s="7" t="n">
+      <c r="E5" s="38" t="n">
         <v>3378.446360574308</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="39" t="n">
         <v>48960377.08851565</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="n">
+      <c r="A6" s="36" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>xpcon-porto-cerro</t>
         </is>
       </c>
-      <c r="C6" s="25" t="n">
+      <c r="C6" s="37" t="n">
         <v>13188.75</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="36" t="n">
         <v>86</v>
       </c>
-      <c r="E6" s="7" t="n">
+      <c r="E6" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="6" t="n"/>
+      <c r="F6" s="39" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="n">
+      <c r="A7" s="36" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="18" t="inlineStr">
         <is>
           <t>wf-aquarius</t>
         </is>
       </c>
-      <c r="C7" s="25" t="n">
+      <c r="C7" s="37" t="n">
         <v>16789.05</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="36" t="n">
         <v>84</v>
       </c>
-      <c r="E7" s="7" t="n">
+      <c r="E7" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="6" t="n"/>
+      <c r="F7" s="39" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="n">
+      <c r="A8" s="36" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>viva4-barra4</t>
         </is>
       </c>
-      <c r="C8" s="25" t="n">
+      <c r="C8" s="37" t="n">
         <v>13223.26</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="36" t="n">
         <v>99</v>
       </c>
-      <c r="E8" s="7" t="n">
+      <c r="E8" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="6" t="n"/>
+      <c r="F8" s="39" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5310,7 +5726,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>PREMISSAS APROVADAS NO GATE</t>
         </is>
@@ -5334,7 +5750,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="18" t="inlineStr">
         <is>
           <t>Tipo de Laje</t>
         </is>
@@ -5351,7 +5767,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="18" t="inlineStr">
         <is>
           <t>Tipo de Fundação</t>
         </is>
@@ -5368,7 +5784,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="A6" s="18" t="inlineStr">
         <is>
           <t>Subsolos</t>
         </is>
@@ -5385,7 +5801,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="A7" s="18" t="inlineStr">
         <is>
           <t>Padrão de Acabamento</t>
         </is>
@@ -5402,7 +5818,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="A8" s="18" t="inlineStr">
         <is>
           <t>Tipo de Fachada</t>
         </is>
@@ -5419,7 +5835,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>Tipo de Esquadria</t>
         </is>
@@ -5436,7 +5852,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="A10" s="18" t="inlineStr">
         <is>
           <t>Tipo de Piso predominante</t>
         </is>
@@ -5453,7 +5869,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="5" t="inlineStr">
+      <c r="A11" s="18" t="inlineStr">
         <is>
           <t>Pintura padrão</t>
         </is>
@@ -5470,7 +5886,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="5" t="inlineStr">
+      <c r="A12" s="18" t="inlineStr">
         <is>
           <t>Climatização</t>
         </is>
@@ -5487,7 +5903,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="5" t="inlineStr">
+      <c r="A13" s="18" t="inlineStr">
         <is>
           <t>Sistema de Pressurização</t>
         </is>
@@ -5504,7 +5920,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>Gerador Dedicado</t>
         </is>
@@ -5521,7 +5937,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="A15" s="18" t="inlineStr">
         <is>
           <t>Piscina</t>
         </is>
@@ -5538,7 +5954,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="A16" s="18" t="inlineStr">
         <is>
           <t>Perdas estimadas (concreto)</t>
         </is>
@@ -5555,7 +5971,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="A17" s="18" t="inlineStr">
         <is>
           <t>Prazo de obra (meses)</t>
         </is>
@@ -5572,7 +5988,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="A18" s="18" t="inlineStr">
         <is>
           <t>BDI total estimado</t>
         </is>
@@ -5589,7 +6005,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="A19" s="18" t="inlineStr">
         <is>
           <t>Encargos (sobre MO)</t>
         </is>
@@ -5606,7 +6022,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="5" t="inlineStr">
+      <c r="A20" s="18" t="inlineStr">
         <is>
           <t>Tempo de protensão (meses)</t>
         </is>
@@ -5623,7 +6039,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="5" t="inlineStr">
+      <c r="A21" s="18" t="inlineStr">
         <is>
           <t>Tipologia predominante</t>
         </is>
@@ -5640,7 +6056,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="5" t="inlineStr">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>Garagem (vagas/UR)</t>
         </is>
@@ -5657,7 +6073,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+      <c r="A23" s="18" t="inlineStr">
         <is>
           <t>Tipo de Contenção</t>
         </is>
@@ -5674,425 +6090,425 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="14" t="inlineStr">
+      <c r="A24" s="26" t="inlineStr">
         <is>
           <t>Fundação</t>
         </is>
       </c>
-      <c r="B24" s="14" t="inlineStr">
+      <c r="B24" s="26" t="inlineStr">
         <is>
           <t>Armação com consideração de aço cortado e dobra em obra com 10% de perda;</t>
         </is>
       </c>
-      <c r="C24" s="14" t="inlineStr">
+      <c r="C24" s="26" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="14" t="inlineStr">
+      <c r="A25" s="26" t="inlineStr">
         <is>
           <t>Fundação</t>
         </is>
       </c>
-      <c r="B25" s="14" t="inlineStr">
+      <c r="B25" s="26" t="inlineStr">
         <is>
           <t>Concreto fck de 30 Mpa para estacas, com 30% de perda;</t>
         </is>
       </c>
-      <c r="C25" s="14" t="inlineStr">
+      <c r="C25" s="26" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="14" t="inlineStr">
+      <c r="A26" s="26" t="inlineStr">
         <is>
           <t>Fundação</t>
         </is>
       </c>
-      <c r="B26" s="14" t="inlineStr">
+      <c r="B26" s="26" t="inlineStr">
         <is>
           <t>Concreto fck de 30 Mpa e 40Mpa em fundação rasa e cortina, com 5% de perda;</t>
         </is>
       </c>
-      <c r="C26" s="14" t="inlineStr">
+      <c r="C26" s="26" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="14" t="inlineStr">
+      <c r="A27" s="26" t="inlineStr">
         <is>
           <t>Fundação</t>
         </is>
       </c>
-      <c r="B27" s="14" t="inlineStr">
+      <c r="B27" s="26" t="inlineStr">
         <is>
           <t>Rebaixamento de lençol freático;</t>
         </is>
       </c>
-      <c r="C27" s="14" t="inlineStr">
+      <c r="C27" s="26" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="14" t="inlineStr">
+      <c r="A28" s="26" t="inlineStr">
         <is>
           <t>Supraestrutura</t>
         </is>
       </c>
-      <c r="B28" s="14" t="inlineStr">
+      <c r="B28" s="26" t="inlineStr">
         <is>
           <t>Armação com aço cortado e dobrado em obra, consideração de 10% de perda;</t>
         </is>
       </c>
-      <c r="C28" s="14" t="inlineStr">
+      <c r="C28" s="26" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="14" t="inlineStr">
+      <c r="A29" s="26" t="inlineStr">
         <is>
           <t>Supraestrutura</t>
         </is>
       </c>
-      <c r="B29" s="14" t="inlineStr">
+      <c r="B29" s="26" t="inlineStr">
         <is>
           <t>Sistema de protensão de vigas;</t>
         </is>
       </c>
-      <c r="C29" s="14" t="inlineStr">
+      <c r="C29" s="26" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="14" t="inlineStr">
+      <c r="A30" s="26" t="inlineStr">
         <is>
           <t>Supraestrutura</t>
         </is>
       </c>
-      <c r="B30" s="14" t="inlineStr">
+      <c r="B30" s="26" t="inlineStr">
         <is>
           <t>Concreto fck de 45 Mpa, incluindo serviço de bombeamento, consideração de 5% de perda;</t>
         </is>
       </c>
-      <c r="C30" s="14" t="inlineStr">
+      <c r="C30" s="26" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="14" t="inlineStr">
+      <c r="A31" s="26" t="inlineStr">
         <is>
           <t>Supraestrutura</t>
         </is>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B31" s="26" t="inlineStr">
         <is>
           <t>Locação de escoramento de metálico;</t>
         </is>
       </c>
-      <c r="C31" s="14" t="inlineStr">
+      <c r="C31" s="26" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="14" t="inlineStr">
+      <c r="A32" s="26" t="inlineStr">
         <is>
           <t>Supraestrutura</t>
         </is>
       </c>
-      <c r="B32" s="14" t="inlineStr">
+      <c r="B32" s="26" t="inlineStr">
         <is>
           <t>Mão de obra de supraestrutura.</t>
         </is>
       </c>
-      <c r="C32" s="14" t="inlineStr">
+      <c r="C32" s="26" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="14" t="inlineStr">
+      <c r="A33" s="26" t="inlineStr">
         <is>
           <t>Instalações</t>
         </is>
       </c>
-      <c r="B33" s="14" t="inlineStr">
+      <c r="B33" s="26" t="inlineStr">
         <is>
           <t>Os valores das instalações, preventivas, hidráulicas, elétricas, gás, SPDA e comunicação foram consideradas através de levantamento de itens de listagem de quantidades dos projetos disponibilizados;</t>
         </is>
       </c>
-      <c r="C33" s="14" t="inlineStr">
+      <c r="C33" s="26" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="14" t="inlineStr">
+      <c r="A34" s="26" t="inlineStr">
         <is>
           <t>Acabamentos</t>
         </is>
       </c>
-      <c r="B34" s="14" t="inlineStr">
+      <c r="B34" s="26" t="inlineStr">
         <is>
           <t>Consideração dos acabamentos conforme áreas de aplicação do modelo;</t>
         </is>
       </c>
-      <c r="C34" s="14" t="inlineStr">
+      <c r="C34" s="26" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="14" t="inlineStr">
+      <c r="A35" s="26" t="inlineStr">
         <is>
           <t>Quantificação</t>
         </is>
       </c>
-      <c r="B35" s="14" t="inlineStr">
+      <c r="B35" s="26" t="inlineStr">
         <is>
           <t>Quantificação seguindo detalhamentos de projeto e resumo de quantitativos com complementação de estimativas devido à ausência de detalhamentos;</t>
         </is>
       </c>
-      <c r="C35" s="14" t="inlineStr">
+      <c r="C35" s="26" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="14" t="inlineStr">
+      <c r="A36" s="26" t="inlineStr">
         <is>
           <t>Quantificação</t>
         </is>
       </c>
-      <c r="B36" s="14" t="inlineStr">
+      <c r="B36" s="26" t="inlineStr">
         <is>
           <t>Levantamento realizado via visus, utilizando arquivo .ifc;</t>
         </is>
       </c>
-      <c r="C36" s="14" t="inlineStr">
+      <c r="C36" s="26" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="14" t="inlineStr">
+      <c r="A37" s="26" t="inlineStr">
         <is>
           <t>Movimentações de Terra</t>
         </is>
       </c>
-      <c r="B37" s="14" t="inlineStr">
+      <c r="B37" s="26" t="inlineStr">
         <is>
           <t>considerando 30% de empolamento;</t>
         </is>
       </c>
-      <c r="C37" s="14" t="inlineStr">
+      <c r="C37" s="26" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="14" t="inlineStr">
+      <c r="A38" s="26" t="inlineStr">
         <is>
           <t>Infraestrutura</t>
         </is>
       </c>
-      <c r="B38" s="14" t="inlineStr">
+      <c r="B38" s="26" t="inlineStr">
         <is>
           <t>consideração de 5% de perda, para fundação rasa – aditivo em reservatórios;</t>
         </is>
       </c>
-      <c r="C38" s="14" t="inlineStr">
+      <c r="C38" s="26" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="14" t="inlineStr">
+      <c r="A39" s="26" t="inlineStr">
         <is>
           <t>Supraestrutura</t>
         </is>
       </c>
-      <c r="B39" s="14" t="inlineStr">
+      <c r="B39" s="26" t="inlineStr">
         <is>
           <t>consideração de 10% de perda;</t>
         </is>
       </c>
-      <c r="C39" s="14" t="inlineStr">
+      <c r="C39" s="26" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="14" t="inlineStr">
+      <c r="A40" s="26" t="inlineStr">
         <is>
           <t>Supraestrutura</t>
         </is>
       </c>
-      <c r="B40" s="14" t="inlineStr">
+      <c r="B40" s="26" t="inlineStr">
         <is>
           <t>consideração de 5% de perda – aditivo em reservatórios;</t>
         </is>
       </c>
-      <c r="C40" s="14" t="inlineStr">
+      <c r="C40" s="26" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="14" t="inlineStr">
+      <c r="A41" s="26" t="inlineStr">
         <is>
           <t>Geral</t>
         </is>
       </c>
-      <c r="B41" s="14" t="inlineStr">
+      <c r="B41" s="26" t="inlineStr">
         <is>
           <t>Custos consideram prazo de obra de 57 meses;</t>
         </is>
       </c>
-      <c r="C41" s="14" t="inlineStr">
+      <c r="C41" s="26" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="14" t="inlineStr">
+      <c r="A42" s="26" t="inlineStr">
         <is>
           <t>Fundação e Supraestrutura</t>
         </is>
       </c>
-      <c r="B42" s="14" t="inlineStr">
+      <c r="B42" s="26" t="inlineStr">
         <is>
           <t>Quantificação seguindo detalhamentos de projeto e resumo de quantitativo disponibilizado</t>
         </is>
       </c>
-      <c r="C42" s="14" t="inlineStr">
+      <c r="C42" s="26" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="14" t="inlineStr">
+      <c r="A43" s="26" t="inlineStr">
         <is>
           <t>Fundação Rasa</t>
         </is>
       </c>
-      <c r="B43" s="14" t="inlineStr">
+      <c r="B43" s="26" t="inlineStr">
         <is>
           <t>Escavação e reaterro de Fundação Rasa</t>
         </is>
       </c>
-      <c r="C43" s="14" t="inlineStr">
+      <c r="C43" s="26" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="14" t="inlineStr">
+      <c r="A44" s="26" t="inlineStr">
         <is>
           <t>Fundação Rasa</t>
         </is>
       </c>
-      <c r="B44" s="14" t="inlineStr">
+      <c r="B44" s="26" t="inlineStr">
         <is>
           <t>Lastro de concreto magro em Fundação Rasa</t>
         </is>
       </c>
-      <c r="C44" s="14" t="inlineStr">
+      <c r="C44" s="26" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="14" t="inlineStr">
+      <c r="A45" s="26" t="inlineStr">
         <is>
           <t>Fundação Rasa</t>
         </is>
       </c>
-      <c r="B45" s="14" t="inlineStr">
+      <c r="B45" s="26" t="inlineStr">
         <is>
           <t>Rebaixamento de lençol freático para o tempo de fundação</t>
         </is>
       </c>
-      <c r="C45" s="14" t="inlineStr">
+      <c r="C45" s="26" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="14" t="inlineStr">
+      <c r="A46" s="26" t="inlineStr">
         <is>
           <t>Infraestrutura</t>
         </is>
       </c>
-      <c r="B46" s="14" t="inlineStr">
+      <c r="B46" s="26" t="inlineStr">
         <is>
           <t>Armação com consideração de aço cortado e dobra em obra com 10% de perda</t>
         </is>
       </c>
-      <c r="C46" s="14" t="inlineStr">
+      <c r="C46" s="26" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="14" t="inlineStr">
+      <c r="A47" s="26" t="inlineStr">
         <is>
           <t>Infraestrutura</t>
         </is>
       </c>
-      <c r="B47" s="14" t="inlineStr">
+      <c r="B47" s="26" t="inlineStr">
         <is>
           <t>Concreto fck de 35 MPa em rasa com 5% de perda</t>
         </is>
       </c>
-      <c r="C47" s="14" t="inlineStr">
+      <c r="C47" s="26" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="14" t="inlineStr">
+      <c r="A48" s="26" t="inlineStr">
         <is>
           <t>Supraestrutura</t>
         </is>
       </c>
-      <c r="B48" s="14" t="inlineStr">
+      <c r="B48" s="26" t="inlineStr">
         <is>
           <t>Fabricação de forma de pilares, vigas, lajes, rampas e escadarias em tábua, considerando 2 jogos</t>
         </is>
       </c>
-      <c r="C48" s="14" t="inlineStr">
+      <c r="C48" s="26" t="inlineStr">
         <is>
           <t>Base qualitativa</t>
         </is>
@@ -6127,7 +6543,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>MOVIMENTAÇÃO DE TERRA — DETALHAMENTO</t>
         </is>
@@ -6136,7 +6552,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total estimado (mediana de 58 similares): R$ 354.844  |  R$/m²: 21.51</t>
+          <t>Total estimado (mediana de 58 similares): R$ 322.586  |  R$/m²: 21.51</t>
         </is>
       </c>
     </row>
@@ -6183,12 +6599,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>(sem detalhamento granular nos similares — usar valor agregado acima)</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr"/>
+      <c r="B5" s="26" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6220,7 +6636,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>INFRAESTRUTURA — DETALHAMENTO</t>
         </is>
@@ -6229,7 +6645,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total estimado (mediana de 63 similares): R$ 3.228.418  |  R$/m²: 195.66</t>
+          <t>Total estimado (mediana de 63 similares): R$ 3.081.672  |  R$/m²: 195.66</t>
         </is>
       </c>
     </row>
@@ -6276,32 +6692,32 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="A5" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>Infraestrutura (canaletas, eletrocalhas, civil leve)</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>vb</t>
         </is>
       </c>
-      <c r="D5" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E5" s="18" t="n">
+      <c r="D5" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" s="28" t="n">
         <v>6000</v>
       </c>
-      <c r="F5" s="19" t="n">
+      <c r="F5" s="29" t="n">
         <v>6000</v>
       </c>
-      <c r="G5" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="16" t="inlineStr">
+      <c r="G5" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
@@ -6323,7 +6739,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -6337,7 +6753,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>SUPRAESTRUTURA — DETALHAMENTO</t>
         </is>
@@ -6346,7 +6762,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total estimado (mediana de 56 similares): R$ 10.843.094  |  R$/m²: 657.16</t>
+          <t>Total estimado (mediana de 56 similares): R$ 10.350.226  |  R$/m²: 657.16</t>
         </is>
       </c>
     </row>
@@ -6393,12 +6809,232 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
-        <is>
-          <t>(sem detalhamento granular nos similares — usar valor agregado acima)</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="inlineStr"/>
+      <c r="A5" s="30" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="31" t="inlineStr">
+        <is>
+          <t>Concreto (ex: Concreto Usinado FCK = 35 | Concreto Usinado FCK = 45)</t>
+        </is>
+      </c>
+      <c r="C5" s="30" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D5" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E5" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="32" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" s="31" t="inlineStr">
+        <is>
+          <t>amalfi-tramonti, fonseca-empreendimentos-estoril, wf-aquarius</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="23" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="24" t="inlineStr">
+        <is>
+          <t>Armadura (ex: Armação Aço CA-50, Diâmet)</t>
+        </is>
+      </c>
+      <c r="C6" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D6" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E6" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F6" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G6" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="24" t="inlineStr">
+        <is>
+          <t>amalfi-tramonti</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="24" t="inlineStr">
+        <is>
+          <t>Execução Estrutural (ex: Mão de obra empreitada pa)</t>
+        </is>
+      </c>
+      <c r="C7" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D7" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E7" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F7" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G7" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="24" t="inlineStr">
+        <is>
+          <t>fonseca-empreendimentos-estoril</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="24" t="inlineStr">
+        <is>
+          <t>Concreto/Fundação (ex: Concreto Usinado bombeáve | Locação de Escoramento Me)</t>
+        </is>
+      </c>
+      <c r="C8" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D8" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="24" t="inlineStr">
+        <is>
+          <t>xpcon-porto-cerro</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="24" t="inlineStr">
+        <is>
+          <t>Superestrutura (ex: Mão de obra para execução)</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D9" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E9" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="24" t="inlineStr">
+        <is>
+          <t>wf-aquarius</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="B10" s="24" t="inlineStr">
+        <is>
+          <t>Concreto e Estrutura (ex: Mão de obra para execução | Concreto Usinado FCK = 35)</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D10" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E10" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="25" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="24" t="inlineStr">
+        <is>
+          <t>viva4-barra4</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6430,7 +7066,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>ALVENARIA — DETALHAMENTO</t>
         </is>
@@ -6486,32 +7122,32 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="A5" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>Dreno de Fundo Anti-turbilhão 1 1/2´´ com Tampa FSB e base em latão para Piscinas de Alvenaria</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="18" t="n">
+      <c r="E5" s="28" t="n">
         <v>776.64</v>
       </c>
-      <c r="F5" s="19" t="n">
+      <c r="F5" s="29" t="n">
         <v>3106.56</v>
       </c>
-      <c r="G5" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="16" t="inlineStr">
+      <c r="G5" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
@@ -6547,7 +7183,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>IMPERMEABILIZAÇÃO — DETALHAMENTO</t>
         </is>
@@ -6556,7 +7192,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total estimado (mediana de 61 similares): R$ 1.009.663  |  R$/m²: 61.19</t>
+          <t>Total estimado (mediana de 61 similares): R$ 963.769  |  R$/m²: 61.19</t>
         </is>
       </c>
     </row>
@@ -6603,12 +7239,12 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="14" t="inlineStr">
+      <c r="A5" s="26" t="inlineStr">
         <is>
           <t>(sem detalhamento granular nos similares — usar valor agregado acima)</t>
         </is>
       </c>
-      <c r="B5" s="14" t="inlineStr"/>
+      <c r="B5" s="26" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -6640,7 +7276,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>INSTALAÇÕES — DETALHAMENTO</t>
         </is>
@@ -6649,7 +7285,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Total estimado (mediana de 80 similares): R$ 4.548.397  |  R$/m²: 275.66</t>
+          <t>Total estimado (mediana de 80 similares): R$ 4.961.887  |  R$/m²: 275.66</t>
         </is>
       </c>
     </row>
@@ -6696,962 +7332,962 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="A5" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>Quadro distrib. chapa pintada - embutir</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>pç</t>
         </is>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="27" t="n">
         <v>112</v>
       </c>
-      <c r="E5" s="18" t="n">
+      <c r="E5" s="28" t="n">
         <v>2210</v>
       </c>
-      <c r="F5" s="19" t="n">
+      <c r="F5" s="29" t="n">
         <v>247520</v>
       </c>
-      <c r="G5" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="16" t="inlineStr">
+      <c r="G5" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="24" t="inlineStr">
         <is>
           <t>viva4-barra4</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="n">
+      <c r="A6" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>Interruptor DR 25A, 30mA, Tipo AC, bipolar</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="27" t="n">
         <v>14</v>
       </c>
-      <c r="E6" s="18" t="n">
+      <c r="E6" s="28" t="n">
         <v>87.76000000000001</v>
       </c>
-      <c r="F6" s="19" t="n">
+      <c r="F6" s="29" t="n">
         <v>1228.64</v>
       </c>
-      <c r="G6" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="16" t="inlineStr">
+      <c r="G6" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="n">
+      <c r="A7" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>Eletroduto PVC flexível - Eletroduto leve - 3/4"</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="27" t="n">
         <v>23784.7</v>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="E7" s="28" t="n">
         <v>3.375</v>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F7" s="29" t="n">
         <v>80273.3625</v>
       </c>
-      <c r="G7" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="G7" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="24" t="inlineStr">
         <is>
           <t>viva4-barra4</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="n">
+      <c r="A8" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>HIDRÔMETROS MULTIJATO CLASSE B DN25 (1") QN: 2,50 M³/H</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="27" t="n">
         <v>113</v>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="28" t="n">
         <v>863.2</v>
       </c>
-      <c r="F8" s="19" t="n">
+      <c r="F8" s="29" t="n">
         <v>97541.60000000001</v>
       </c>
-      <c r="G8" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="G8" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="n">
+      <c r="A9" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="24" t="inlineStr">
         <is>
           <t>Eletroduto PVC flexível - Eletroduto pesado - 1.1/4"</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="27" t="n">
         <v>8052</v>
       </c>
-      <c r="E9" s="18" t="n">
+      <c r="E9" s="28" t="n">
         <v>9.1</v>
       </c>
-      <c r="F9" s="19" t="n">
+      <c r="F9" s="29" t="n">
         <v>73273.2</v>
       </c>
-      <c r="G9" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="16" t="inlineStr">
+      <c r="G9" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="24" t="inlineStr">
         <is>
           <t>viva4-barra4</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="n">
+      <c r="A10" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="24" t="inlineStr">
         <is>
           <t>DPS Classe 2 275V/20kA Tripolar</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D10" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="18" t="n">
+      <c r="D10" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="28" t="n">
         <v>400.8</v>
       </c>
-      <c r="F10" s="19" t="n">
+      <c r="F10" s="29" t="n">
         <v>400.8</v>
       </c>
-      <c r="G10" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="16" t="inlineStr">
+      <c r="G10" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="n">
+      <c r="A11" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>Quadro de distribuição, 500x1000x120mm</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="27" t="n">
         <v>109</v>
       </c>
-      <c r="E11" s="18" t="n">
+      <c r="E11" s="28" t="n">
         <v>730.3099999999999</v>
       </c>
-      <c r="F11" s="19" t="n">
+      <c r="F11" s="29" t="n">
         <v>79603.78999999999</v>
       </c>
-      <c r="G11" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="16" t="inlineStr">
+      <c r="G11" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="n">
+      <c r="A12" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t>TUBO PVC ESG SN DN100</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="27" t="n">
         <v>4289.45</v>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="E12" s="28" t="n">
         <v>14.15</v>
       </c>
-      <c r="F12" s="19" t="n">
+      <c r="F12" s="29" t="n">
         <v>60695.7175</v>
       </c>
-      <c r="G12" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="16" t="inlineStr">
+      <c r="G12" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="n">
+      <c r="A13" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="24" t="inlineStr">
         <is>
           <t>TUBO CPVC DN28</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="27" t="n">
         <v>1396.1</v>
       </c>
-      <c r="E13" s="18" t="n">
+      <c r="E13" s="28" t="n">
         <v>40.9</v>
       </c>
-      <c r="F13" s="19" t="n">
+      <c r="F13" s="29" t="n">
         <v>57100.48999999999</v>
       </c>
-      <c r="G13" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="16" t="inlineStr">
+      <c r="G13" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="n">
+      <c r="A14" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="24" t="inlineStr">
         <is>
           <t>Caixa de Luz 4''x4'', de embutir, em PVC para eletroduto corrugado</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="27" t="n">
         <v>46</v>
       </c>
-      <c r="E14" s="18" t="n">
+      <c r="E14" s="28" t="n">
         <v>1418.66</v>
       </c>
-      <c r="F14" s="19" t="n">
+      <c r="F14" s="29" t="n">
         <v>65258.36</v>
       </c>
-      <c r="G14" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="16" t="inlineStr">
+      <c r="G14" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="n">
+      <c r="A15" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="24" t="inlineStr">
         <is>
           <t>Transformador a seco 500 kVA – IP00</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D15" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="18" t="n">
+      <c r="D15" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="28" t="n">
         <v>65000</v>
       </c>
-      <c r="F15" s="19" t="n">
+      <c r="F15" s="29" t="n">
         <v>65000</v>
       </c>
-      <c r="G15" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="16" t="inlineStr">
+      <c r="G15" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="n">
+      <c r="A16" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B16" s="24" t="inlineStr">
         <is>
           <t>TUBO PVC SOLD DN 25</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="D16" s="27" t="n">
         <v>20157.9</v>
       </c>
-      <c r="E16" s="18" t="n">
+      <c r="E16" s="28" t="n">
         <v>2.75</v>
       </c>
-      <c r="F16" s="19" t="n">
+      <c r="F16" s="29" t="n">
         <v>55434.22500000001</v>
       </c>
-      <c r="G16" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="16" t="inlineStr">
+      <c r="G16" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="n">
+      <c r="A17" s="23" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="24" t="inlineStr">
         <is>
           <t>Disjuntor Caixa Moldada Tripolar 90A, Curva C, 250/440V 6kA</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D17" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="18" t="n">
+      <c r="D17" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="28" t="n">
         <v>306.89</v>
       </c>
-      <c r="F17" s="19" t="n">
+      <c r="F17" s="29" t="n">
         <v>306.89</v>
       </c>
-      <c r="G17" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="16" t="inlineStr">
+      <c r="G17" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="15" t="n">
+      <c r="A18" s="23" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="16" t="inlineStr">
+      <c r="B18" s="24" t="inlineStr">
         <is>
           <t>TUBO CPVC DN22</t>
         </is>
       </c>
-      <c r="C18" s="15" t="inlineStr">
+      <c r="C18" s="23" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="D18" s="17" t="n">
+      <c r="D18" s="27" t="n">
         <v>2111.3</v>
       </c>
-      <c r="E18" s="18" t="n">
+      <c r="E18" s="28" t="n">
         <v>24.39</v>
       </c>
-      <c r="F18" s="19" t="n">
+      <c r="F18" s="29" t="n">
         <v>51494.607</v>
       </c>
-      <c r="G18" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" s="16" t="inlineStr">
+      <c r="G18" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="n">
+      <c r="A19" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>Mão de obra instalações SPDA</t>
         </is>
       </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>Unid.</t>
         </is>
       </c>
-      <c r="D19" s="17" t="n">
+      <c r="D19" s="27" t="n">
         <v>14491.98</v>
       </c>
-      <c r="E19" s="18" t="n">
+      <c r="E19" s="28" t="n">
         <v>4</v>
       </c>
-      <c r="F19" s="19" t="n">
+      <c r="F19" s="29" t="n">
         <v>57967.92</v>
       </c>
-      <c r="G19" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="16" t="inlineStr">
+      <c r="G19" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="15" t="n">
+      <c r="A20" s="23" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="16" t="inlineStr">
+      <c r="B20" s="24" t="inlineStr">
         <is>
           <t>Caixa de Passagem de sobrepor, 500x500x400mm, fabricado em PVC antichamas</t>
         </is>
       </c>
-      <c r="C20" s="15" t="inlineStr">
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D20" s="17" t="n">
+      <c r="D20" s="27" t="n">
         <v>57</v>
       </c>
-      <c r="E20" s="18" t="n">
+      <c r="E20" s="28" t="n">
         <v>921.96</v>
       </c>
-      <c r="F20" s="19" t="n">
+      <c r="F20" s="29" t="n">
         <v>52551.72</v>
       </c>
-      <c r="G20" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H20" s="16" t="inlineStr">
+      <c r="G20" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H20" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="n">
+      <c r="A21" s="23" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="24" t="inlineStr">
         <is>
           <t>Transformador a seco 225 kVA – IP00</t>
         </is>
       </c>
-      <c r="C21" s="15" t="inlineStr">
+      <c r="C21" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D21" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="18" t="n">
+      <c r="D21" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="28" t="n">
         <v>52000</v>
       </c>
-      <c r="F21" s="19" t="n">
+      <c r="F21" s="29" t="n">
         <v>52000</v>
       </c>
-      <c r="G21" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H21" s="16" t="inlineStr">
+      <c r="G21" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H21" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="n">
+      <c r="A22" s="23" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B22" s="24" t="inlineStr">
         <is>
           <t>MISTURADOR MONOCOMANDO Ø3/4"</t>
         </is>
       </c>
-      <c r="C22" s="15" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D22" s="17" t="n">
+      <c r="D22" s="27" t="n">
         <v>206</v>
       </c>
-      <c r="E22" s="18" t="n">
+      <c r="E22" s="28" t="n">
         <v>239.9</v>
       </c>
-      <c r="F22" s="19" t="n">
+      <c r="F22" s="29" t="n">
         <v>49419.4</v>
       </c>
-      <c r="G22" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="16" t="inlineStr">
+      <c r="G22" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="n">
+      <c r="A23" s="23" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B23" s="24" t="inlineStr">
         <is>
           <t>Disjuntor Tripolar Termomagnético -
 norma DIN (Curva C) - 125 A - 10 kA</t>
         </is>
       </c>
-      <c r="C23" s="15" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>pç</t>
         </is>
       </c>
-      <c r="D23" s="17" t="n">
+      <c r="D23" s="27" t="n">
         <v>27</v>
       </c>
-      <c r="E23" s="18" t="n">
+      <c r="E23" s="28" t="n">
         <v>1534.495</v>
       </c>
-      <c r="F23" s="19" t="n">
+      <c r="F23" s="29" t="n">
         <v>41431.365</v>
       </c>
-      <c r="G23" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H23" s="16" t="inlineStr">
+      <c r="G23" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H23" s="24" t="inlineStr">
         <is>
           <t>viva4-barra4</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="n">
+      <c r="A24" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B24" s="24" t="inlineStr">
         <is>
           <t>Barramento Blindado BWW01-MA250J-54</t>
         </is>
       </c>
-      <c r="C24" s="15" t="inlineStr">
+      <c r="C24" s="23" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="D24" s="17" t="n">
+      <c r="D24" s="27" t="n">
         <v>142</v>
       </c>
-      <c r="E24" s="18" t="n">
+      <c r="E24" s="28" t="n">
         <v>320</v>
       </c>
-      <c r="F24" s="19" t="n">
+      <c r="F24" s="29" t="n">
         <v>45440</v>
       </c>
-      <c r="G24" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H24" s="16" t="inlineStr">
+      <c r="G24" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H24" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="n">
+      <c r="A25" s="23" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="16" t="inlineStr">
+      <c r="B25" s="24" t="inlineStr">
         <is>
           <t>Quadro de destribuição varíavel</t>
         </is>
       </c>
-      <c r="C25" s="15" t="inlineStr">
+      <c r="C25" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D25" s="17" t="n">
+      <c r="D25" s="27" t="n">
         <v>76</v>
       </c>
-      <c r="E25" s="18" t="n">
+      <c r="E25" s="28" t="n">
         <v>486.87</v>
       </c>
-      <c r="F25" s="19" t="n">
+      <c r="F25" s="29" t="n">
         <v>37002.12</v>
       </c>
-      <c r="G25" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" s="16" t="inlineStr">
+      <c r="G25" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="n">
+      <c r="A26" s="23" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B26" s="24" t="inlineStr">
         <is>
           <t>TUBO PVC ESG SR DN100</t>
         </is>
       </c>
-      <c r="C26" s="15" t="inlineStr">
+      <c r="C26" s="23" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="D26" s="17" t="n">
+      <c r="D26" s="27" t="n">
         <v>1083.88</v>
       </c>
-      <c r="E26" s="18" t="n">
+      <c r="E26" s="28" t="n">
         <v>28.39</v>
       </c>
-      <c r="F26" s="19" t="n">
+      <c r="F26" s="29" t="n">
         <v>30771.35320000001</v>
       </c>
-      <c r="G26" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="16" t="inlineStr">
+      <c r="G26" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="n">
+      <c r="A27" s="23" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="16" t="inlineStr">
+      <c r="B27" s="24" t="inlineStr">
         <is>
           <t>CABO DE COBRE NU 70MM² – 7 FIOS</t>
         </is>
       </c>
-      <c r="C27" s="15" t="inlineStr">
+      <c r="C27" s="23" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="D27" s="17" t="n">
+      <c r="D27" s="27" t="n">
         <v>583.41</v>
       </c>
-      <c r="E27" s="18" t="n">
+      <c r="E27" s="28" t="n">
         <v>59.39</v>
       </c>
-      <c r="F27" s="19" t="n">
+      <c r="F27" s="29" t="n">
         <v>34648.7199</v>
       </c>
-      <c r="G27" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H27" s="16" t="inlineStr">
+      <c r="G27" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H27" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="n">
+      <c r="A28" s="23" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="16" t="inlineStr">
+      <c r="B28" s="24" t="inlineStr">
         <is>
           <t>Mini Disjuntor Monopolar 16A, Curva C, 250/440V 3kA</t>
         </is>
       </c>
-      <c r="C28" s="15" t="inlineStr">
+      <c r="C28" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D28" s="17" t="n">
+      <c r="D28" s="27" t="n">
         <v>15</v>
       </c>
-      <c r="E28" s="18" t="n">
+      <c r="E28" s="28" t="n">
         <v>11.4</v>
       </c>
-      <c r="F28" s="19" t="n">
+      <c r="F28" s="29" t="n">
         <v>171</v>
       </c>
-      <c r="G28" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" s="16" t="inlineStr">
+      <c r="G28" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="n">
+      <c r="A29" s="23" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="16" t="inlineStr">
+      <c r="B29" s="24" t="inlineStr">
         <is>
           <t>Mini Disjuntor Monopolar 10A, Curva C, 250/440V 3kA</t>
         </is>
       </c>
-      <c r="C29" s="15" t="inlineStr">
+      <c r="C29" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D29" s="17" t="n">
+      <c r="D29" s="27" t="n">
         <v>21</v>
       </c>
-      <c r="E29" s="18" t="n">
+      <c r="E29" s="28" t="n">
         <v>7.91</v>
       </c>
-      <c r="F29" s="19" t="n">
+      <c r="F29" s="29" t="n">
         <v>166.11</v>
       </c>
-      <c r="G29" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" s="16" t="inlineStr">
+      <c r="G29" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="n">
+      <c r="A30" s="23" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="16" t="inlineStr">
+      <c r="B30" s="24" t="inlineStr">
         <is>
           <t>Interruptor bipolar DR (fase/neutro - In
 30mA) - DIN - 40 A</t>
         </is>
       </c>
-      <c r="C30" s="15" t="inlineStr">
+      <c r="C30" s="23" t="inlineStr">
         <is>
           <t>pç</t>
         </is>
       </c>
-      <c r="D30" s="17" t="n">
+      <c r="D30" s="27" t="n">
         <v>186</v>
       </c>
-      <c r="E30" s="18" t="n">
+      <c r="E30" s="28" t="n">
         <v>168.99</v>
       </c>
-      <c r="F30" s="19" t="n">
+      <c r="F30" s="29" t="n">
         <v>31432.14</v>
       </c>
-      <c r="G30" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" s="16" t="inlineStr">
+      <c r="G30" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="24" t="inlineStr">
         <is>
           <t>viva4-barra4</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="n">
+      <c r="A31" s="23" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="16" t="inlineStr">
+      <c r="B31" s="24" t="inlineStr">
         <is>
           <t>REGISTRO DE GAVETA Ø3/4"</t>
         </is>
       </c>
-      <c r="C31" s="15" t="inlineStr">
+      <c r="C31" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D31" s="17" t="n">
+      <c r="D31" s="27" t="n">
         <v>867</v>
       </c>
-      <c r="E31" s="18" t="n">
+      <c r="E31" s="28" t="n">
         <v>31.72</v>
       </c>
-      <c r="F31" s="19" t="n">
+      <c r="F31" s="29" t="n">
         <v>27501.24</v>
       </c>
-      <c r="G31" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" s="16" t="inlineStr">
+      <c r="G31" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="n">
+      <c r="A32" s="23" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="16" t="inlineStr">
+      <c r="B32" s="24" t="inlineStr">
         <is>
           <t>Interruptor tetrapolar DR (3 fases/neutro - In 30mA) - DIN - 63 A</t>
         </is>
       </c>
-      <c r="C32" s="15" t="inlineStr">
+      <c r="C32" s="23" t="inlineStr">
         <is>
           <t>pç</t>
         </is>
       </c>
-      <c r="D32" s="17" t="n">
+      <c r="D32" s="27" t="n">
         <v>102</v>
       </c>
-      <c r="E32" s="18" t="n">
+      <c r="E32" s="28" t="n">
         <v>252.89</v>
       </c>
-      <c r="F32" s="19" t="n">
+      <c r="F32" s="29" t="n">
         <v>25794.78</v>
       </c>
-      <c r="G32" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" s="16" t="inlineStr">
+      <c r="G32" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="24" t="inlineStr">
         <is>
           <t>viva4-barra4</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="n">
+      <c r="A33" s="23" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="16" t="inlineStr">
+      <c r="B33" s="24" t="inlineStr">
         <is>
           <t>S/ placa - Tomada hexagonal (NBR 14136) 2P+T 10A</t>
         </is>
       </c>
-      <c r="C33" s="15" t="inlineStr">
+      <c r="C33" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D33" s="17" t="n">
+      <c r="D33" s="27" t="n">
         <v>3059</v>
       </c>
-      <c r="E33" s="18" t="n">
+      <c r="E33" s="28" t="n">
         <v>7.9</v>
       </c>
-      <c r="F33" s="19" t="n">
+      <c r="F33" s="29" t="n">
         <v>24166.1</v>
       </c>
-      <c r="G33" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" s="16" t="inlineStr">
+      <c r="G33" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="24" t="inlineStr">
         <is>
           <t>viva4-barra4</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="n">
+      <c r="A34" s="23" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="16" t="inlineStr">
+      <c r="B34" s="24" t="inlineStr">
         <is>
           <t>CONECT TRANS FM SUPER CPVC DN22X1/2 CB</t>
         </is>
       </c>
-      <c r="C34" s="15" t="inlineStr">
+      <c r="C34" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D34" s="17" t="n">
+      <c r="D34" s="27" t="n">
         <v>1268</v>
       </c>
-      <c r="E34" s="18" t="n">
+      <c r="E34" s="28" t="n">
         <v>19.04</v>
       </c>
-      <c r="F34" s="19" t="n">
+      <c r="F34" s="29" t="n">
         <v>24142.72</v>
       </c>
-      <c r="G34" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" s="16" t="inlineStr">
+      <c r="G34" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
@@ -7687,7 +8323,7 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="13" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>SISTEMAS ESPECIAIS — DETALHAMENTO</t>
         </is>
@@ -7743,964 +8379,964 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="A5" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>PISCINA ADULTA 1</t>
         </is>
       </c>
-      <c r="C5" s="15" t="inlineStr">
+      <c r="C5" s="23" t="inlineStr">
         <is>
           <t>1.1999999999999993</t>
         </is>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="27" t="n">
         <v>61.92</v>
       </c>
-      <c r="E5" s="18" t="n">
+      <c r="E5" s="28" t="n">
         <v>74.30399999999996</v>
       </c>
-      <c r="F5" s="19" t="n">
+      <c r="F5" s="29" t="n">
         <v>4600.903679999998</v>
       </c>
-      <c r="G5" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" s="16" t="inlineStr">
+      <c r="G5" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" s="24" t="inlineStr">
         <is>
           <t>viva4-barra4</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="15" t="n">
+      <c r="A6" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>Gerador de Energia a Diesel 33kva Bifásico 110/220v Silenciado com QTA - Nagano</t>
         </is>
       </c>
-      <c r="C6" s="15" t="inlineStr">
+      <c r="C6" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D6" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E6" s="18" t="n">
+      <c r="D6" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E6" s="28" t="n">
         <v>37800</v>
       </c>
-      <c r="F6" s="19" t="n">
+      <c r="F6" s="29" t="n">
         <v>37800</v>
       </c>
-      <c r="G6" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" s="16" t="inlineStr">
+      <c r="G6" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="15" t="n">
+      <c r="A7" s="23" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>KIT FP-6-2-SI FONTE INTERATIVA COM 6 JATOS</t>
         </is>
       </c>
-      <c r="C7" s="15" t="inlineStr">
+      <c r="C7" s="23" t="inlineStr">
         <is>
           <t>pç</t>
         </is>
       </c>
-      <c r="D7" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E7" s="18" t="n">
+      <c r="D7" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="28" t="n">
         <v>35200</v>
       </c>
-      <c r="F7" s="19" t="n">
+      <c r="F7" s="29" t="n">
         <v>35200</v>
       </c>
-      <c r="G7" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" s="16" t="inlineStr">
+      <c r="G7" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" s="24" t="inlineStr">
         <is>
           <t>xpcon-porto-cerro</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="15" t="n">
+      <c r="A8" s="23" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="16" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>Aquecedor para Piscina -Trocador de calor TH-60 Para Piscinas De Até 50 Mil Litros - Sodramar
 SODRAMAR</t>
         </is>
       </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="C8" s="23" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="D8" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="18" t="n">
+      <c r="D8" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="28" t="n">
         <v>18770</v>
       </c>
-      <c r="F8" s="19" t="n">
+      <c r="F8" s="29" t="n">
         <v>18770</v>
       </c>
-      <c r="G8" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" s="16" t="inlineStr">
+      <c r="G8" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="n">
+      <c r="A9" s="23" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="24" t="inlineStr">
         <is>
           <t>trocador de Calor TIV Para Piscinas - Sodramar (Full Inverter) tiv-45</t>
         </is>
       </c>
-      <c r="C9" s="15" t="inlineStr">
+      <c r="C9" s="23" t="inlineStr">
         <is>
           <t>pç</t>
         </is>
       </c>
-      <c r="D9" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="18" t="n">
+      <c r="D9" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="28" t="n">
         <v>16200</v>
       </c>
-      <c r="F9" s="19" t="n">
+      <c r="F9" s="29" t="n">
         <v>16200</v>
       </c>
-      <c r="G9" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" s="16" t="inlineStr">
+      <c r="G9" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" s="24" t="inlineStr">
         <is>
           <t>xpcon-porto-cerro</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="15" t="n">
+      <c r="A10" s="23" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="24" t="inlineStr">
         <is>
           <t>Aquecedor para Piscina - Trocador de calor TH-25 Para Piscinas De Até 22 Mil Litros - Sodramar
 SODRAMAR</t>
         </is>
       </c>
-      <c r="C10" s="15" t="inlineStr">
+      <c r="C10" s="23" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="D10" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="18" t="n">
+      <c r="D10" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E10" s="28" t="n">
         <v>12657</v>
       </c>
-      <c r="F10" s="19" t="n">
+      <c r="F10" s="29" t="n">
         <v>12657</v>
       </c>
-      <c r="G10" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" s="16" t="inlineStr">
+      <c r="G10" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="15" t="n">
+      <c r="A11" s="23" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="16" t="inlineStr">
+      <c r="B11" s="24" t="inlineStr">
         <is>
           <t>Mão de obra para instalação</t>
         </is>
       </c>
-      <c r="C11" s="15" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>vb</t>
         </is>
       </c>
-      <c r="D11" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="18" t="n">
+      <c r="D11" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="28" t="n">
         <v>10304.38666666667</v>
       </c>
-      <c r="F11" s="19" t="n">
+      <c r="F11" s="29" t="n">
         <v>10304.38666666667</v>
       </c>
-      <c r="G11" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="16" t="inlineStr">
+      <c r="G11" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="n">
+      <c r="A12" s="23" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="16" t="inlineStr">
+      <c r="B12" s="24" t="inlineStr">
         <is>
           <t>SDAI - Acionador manual + avisador audio visual de alarme</t>
         </is>
       </c>
-      <c r="C12" s="15" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="27" t="n">
         <v>37</v>
       </c>
-      <c r="E12" s="18" t="n">
+      <c r="E12" s="28" t="n">
         <v>201.98</v>
       </c>
-      <c r="F12" s="19" t="n">
+      <c r="F12" s="29" t="n">
         <v>7473.26</v>
       </c>
-      <c r="G12" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" s="16" t="inlineStr">
+      <c r="G12" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="15" t="n">
+      <c r="A13" s="23" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B13" s="24" t="inlineStr">
         <is>
           <t>GERADOR DE CLORO SODRAMAR MOD.GS 42-220V</t>
         </is>
       </c>
-      <c r="C13" s="15" t="inlineStr">
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>pç</t>
         </is>
       </c>
-      <c r="D13" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="18" t="n">
+      <c r="D13" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" s="28" t="n">
         <v>7409</v>
       </c>
-      <c r="F13" s="19" t="n">
+      <c r="F13" s="29" t="n">
         <v>7409</v>
       </c>
-      <c r="G13" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" s="16" t="inlineStr">
+      <c r="G13" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" s="24" t="inlineStr">
         <is>
           <t>xpcon-porto-cerro</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="15" t="n">
+      <c r="A14" s="23" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="16" t="inlineStr">
+      <c r="B14" s="24" t="inlineStr">
         <is>
           <t>Gerador de Cloro à base sal com capacidade de gerar 20g de cloro puro por hora</t>
         </is>
       </c>
-      <c r="C14" s="15" t="inlineStr">
+      <c r="C14" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="27" t="n">
         <v>1.5</v>
       </c>
-      <c r="E14" s="18" t="n">
+      <c r="E14" s="28" t="n">
         <v>4170</v>
       </c>
-      <c r="F14" s="19" t="n">
+      <c r="F14" s="29" t="n">
         <v>6255</v>
       </c>
-      <c r="G14" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" s="16" t="inlineStr">
+      <c r="G14" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="15" t="n">
+      <c r="A15" s="23" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="16" t="inlineStr">
+      <c r="B15" s="24" t="inlineStr">
         <is>
           <t>PISCINA INFANTIL</t>
         </is>
       </c>
-      <c r="C15" s="15" t="inlineStr">
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>0.6500000000000004</t>
         </is>
       </c>
-      <c r="D15" s="17" t="n">
+      <c r="D15" s="27" t="n">
         <v>7.62</v>
       </c>
-      <c r="E15" s="18" t="n">
+      <c r="E15" s="28" t="n">
         <v>4.953000000000003</v>
       </c>
-      <c r="F15" s="19" t="n">
+      <c r="F15" s="29" t="n">
         <v>37.74186000000002</v>
       </c>
-      <c r="G15" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" s="16" t="inlineStr">
+      <c r="G15" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" s="24" t="inlineStr">
         <is>
           <t>viva4-barra4</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="15" t="n">
+      <c r="A16" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="16" t="inlineStr">
+      <c r="B16" s="24" t="inlineStr">
         <is>
           <t>MOTOBOMBA SYLLENT AUTO ESCORVANTE 1/3CV Mono</t>
         </is>
       </c>
-      <c r="C16" s="15" t="inlineStr">
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D16" s="17" t="n">
+      <c r="D16" s="27" t="n">
         <v>4</v>
       </c>
-      <c r="E16" s="18" t="n">
+      <c r="E16" s="28" t="n">
         <v>1166</v>
       </c>
-      <c r="F16" s="19" t="n">
+      <c r="F16" s="29" t="n">
         <v>4664</v>
       </c>
-      <c r="G16" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" s="16" t="inlineStr">
+      <c r="G16" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" s="24" t="inlineStr">
         <is>
           <t>wf-aquarius</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="15" t="n">
+      <c r="A17" s="23" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="16" t="inlineStr">
+      <c r="B17" s="24" t="inlineStr">
         <is>
           <t>Material hidráulico e elétrico</t>
         </is>
       </c>
-      <c r="C17" s="15" t="inlineStr">
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>vb</t>
         </is>
       </c>
-      <c r="D17" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E17" s="18" t="n">
+      <c r="D17" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" s="28" t="n">
         <v>4121.754666666668</v>
       </c>
-      <c r="F17" s="19" t="n">
+      <c r="F17" s="29" t="n">
         <v>4121.754666666668</v>
       </c>
-      <c r="G17" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" s="16" t="inlineStr">
+      <c r="G17" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="20" t="n">
+      <c r="A18" s="30" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="21" t="inlineStr">
+      <c r="B18" s="31" t="inlineStr">
         <is>
           <t>GERADOR DE COLORO BZ -30</t>
         </is>
       </c>
-      <c r="C18" s="20" t="inlineStr">
+      <c r="C18" s="30" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D18" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" s="23" t="n">
+      <c r="D18" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" s="34" t="n">
         <v>3656.75</v>
       </c>
-      <c r="F18" s="24" t="n">
+      <c r="F18" s="35" t="n">
         <v>3656.75</v>
       </c>
-      <c r="G18" s="20" t="n">
+      <c r="G18" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="H18" s="21" t="inlineStr">
+      <c r="H18" s="31" t="inlineStr">
         <is>
           <t>amalfi-tramonti, viva4-barra4, wf-aquarius</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="n">
+      <c r="A19" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="16" t="inlineStr">
+      <c r="B19" s="24" t="inlineStr">
         <is>
           <t>MOTOBOMBA SYLLENT AUTO ESCORVANTE 3/4CV Mono</t>
         </is>
       </c>
-      <c r="C19" s="15" t="inlineStr">
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D19" s="17" t="n">
+      <c r="D19" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="E19" s="18" t="n">
+      <c r="E19" s="28" t="n">
         <v>1699</v>
       </c>
-      <c r="F19" s="19" t="n">
+      <c r="F19" s="29" t="n">
         <v>3398</v>
       </c>
-      <c r="G19" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" s="16" t="inlineStr">
+      <c r="G19" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" s="24" t="inlineStr">
         <is>
           <t>wf-aquarius</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="20" t="n">
+      <c r="A20" s="30" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="21" t="inlineStr">
+      <c r="B20" s="31" t="inlineStr">
         <is>
           <t>GERADOR DE COLORO BZ -20</t>
         </is>
       </c>
-      <c r="C20" s="20" t="inlineStr">
+      <c r="C20" s="30" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D20" s="22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" s="23" t="n">
+      <c r="D20" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" s="34" t="n">
         <v>3296.12</v>
       </c>
-      <c r="F20" s="24" t="n">
+      <c r="F20" s="35" t="n">
         <v>3296.12</v>
       </c>
-      <c r="G20" s="20" t="n">
+      <c r="G20" s="30" t="n">
         <v>3</v>
       </c>
-      <c r="H20" s="21" t="inlineStr">
+      <c r="H20" s="31" t="inlineStr">
         <is>
           <t>amalfi-tramonti, viva4-barra4, wf-aquarius</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="15" t="n">
+      <c r="A21" s="23" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="16" t="inlineStr">
+      <c r="B21" s="24" t="inlineStr">
         <is>
           <t>TAMPA ARTICULADA GDA 110X110cm CÓDIGO 3140</t>
         </is>
       </c>
-      <c r="C21" s="15" t="inlineStr">
+      <c r="C21" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D21" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" s="18" t="n">
+      <c r="D21" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" s="28" t="n">
         <v>3200</v>
       </c>
-      <c r="F21" s="19" t="n">
+      <c r="F21" s="29" t="n">
         <v>3200</v>
       </c>
-      <c r="G21" s="15" t="n">
+      <c r="G21" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="H21" s="16" t="inlineStr">
+      <c r="H21" s="24" t="inlineStr">
         <is>
           <t>viva4-barra4, wf-aquarius</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="15" t="n">
+      <c r="A22" s="23" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="16" t="inlineStr">
+      <c r="B22" s="24" t="inlineStr">
         <is>
           <t>Refletor em LED 20W RGB c/ ângulo 150º, encaixe em tubo de 25mm com vedação total d’água em Viton, em aço inox 316 (Inox Puro), com lente em policarbonato</t>
         </is>
       </c>
-      <c r="C22" s="15" t="inlineStr">
+      <c r="C22" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D22" s="17" t="n">
+      <c r="D22" s="27" t="n">
         <v>7</v>
       </c>
-      <c r="E22" s="18" t="n">
+      <c r="E22" s="28" t="n">
         <v>426</v>
       </c>
-      <c r="F22" s="19" t="n">
+      <c r="F22" s="29" t="n">
         <v>2982</v>
       </c>
-      <c r="G22" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H22" s="16" t="inlineStr">
+      <c r="G22" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H22" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="15" t="n">
+      <c r="A23" s="23" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="16" t="inlineStr">
+      <c r="B23" s="24" t="inlineStr">
         <is>
           <t>TAMPA GDA REBAIXADA C/ GRELHA 80X80cm CÓDIGO 3078</t>
         </is>
       </c>
-      <c r="C23" s="15" t="inlineStr">
+      <c r="C23" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D23" s="17" t="n">
+      <c r="D23" s="27" t="n">
         <v>1.5</v>
       </c>
-      <c r="E23" s="18" t="n">
+      <c r="E23" s="28" t="n">
         <v>1850</v>
       </c>
-      <c r="F23" s="19" t="n">
+      <c r="F23" s="29" t="n">
         <v>2775</v>
       </c>
-      <c r="G23" s="15" t="n">
+      <c r="G23" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="H23" s="16" t="inlineStr">
+      <c r="H23" s="24" t="inlineStr">
         <is>
           <t>viva4-barra4, wf-aquarius</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="15" t="n">
+      <c r="A24" s="23" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="16" t="inlineStr">
+      <c r="B24" s="24" t="inlineStr">
         <is>
           <t>Bomba 3/4 cv BM-75 p/ piscinas de até 78 mil litros
 SODAMAR</t>
         </is>
       </c>
-      <c r="C24" s="15" t="inlineStr">
+      <c r="C24" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D24" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" s="18" t="n">
+      <c r="D24" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" s="28" t="n">
         <v>2099</v>
       </c>
-      <c r="F24" s="19" t="n">
+      <c r="F24" s="29" t="n">
         <v>2099</v>
       </c>
-      <c r="G24" s="15" t="n">
+      <c r="G24" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="H24" s="16" t="inlineStr">
+      <c r="H24" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti, viva4-barra4</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="15" t="n">
+      <c r="A25" s="23" t="n">
         <v>21</v>
       </c>
-      <c r="B25" s="16" t="inlineStr">
+      <c r="B25" s="24" t="inlineStr">
         <is>
           <t>SDAI - Repetidora de central de alarme endereçavel</t>
         </is>
       </c>
-      <c r="C25" s="15" t="inlineStr">
+      <c r="C25" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D25" s="17" t="n">
+      <c r="D25" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="E25" s="18" t="n">
+      <c r="E25" s="28" t="n">
         <v>1048.76</v>
       </c>
-      <c r="F25" s="19" t="n">
+      <c r="F25" s="29" t="n">
         <v>2097.52</v>
       </c>
-      <c r="G25" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H25" s="16" t="inlineStr">
+      <c r="G25" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H25" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="15" t="n">
+      <c r="A26" s="23" t="n">
         <v>22</v>
       </c>
-      <c r="B26" s="16" t="inlineStr">
+      <c r="B26" s="24" t="inlineStr">
         <is>
           <t>SDAI - Central de alarme endereçavel</t>
         </is>
       </c>
-      <c r="C26" s="15" t="inlineStr">
+      <c r="C26" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D26" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" s="18" t="n">
+      <c r="D26" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" s="28" t="n">
         <v>2068.81</v>
       </c>
-      <c r="F26" s="19" t="n">
+      <c r="F26" s="29" t="n">
         <v>2068.81</v>
       </c>
-      <c r="G26" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H26" s="16" t="inlineStr">
+      <c r="G26" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H26" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="n">
+      <c r="A27" s="23" t="n">
         <v>23</v>
       </c>
-      <c r="B27" s="16" t="inlineStr">
+      <c r="B27" s="24" t="inlineStr">
         <is>
           <t>Filtro para piscina FM-50 p/ até 78 mil litros
 SODAMAR</t>
         </is>
       </c>
-      <c r="C27" s="15" t="inlineStr">
+      <c r="C27" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D27" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" s="18" t="n">
+      <c r="D27" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" s="28" t="n">
         <v>1628</v>
       </c>
-      <c r="F27" s="19" t="n">
+      <c r="F27" s="29" t="n">
         <v>1628</v>
       </c>
-      <c r="G27" s="15" t="n">
+      <c r="G27" s="23" t="n">
         <v>2</v>
       </c>
-      <c r="H27" s="16" t="inlineStr">
+      <c r="H27" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti, viva4-barra4</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="15" t="n">
+      <c r="A28" s="23" t="n">
         <v>24</v>
       </c>
-      <c r="B28" s="16" t="inlineStr">
+      <c r="B28" s="24" t="inlineStr">
         <is>
           <t>MOTOBOMBA SODRAMAR BMP-25</t>
         </is>
       </c>
-      <c r="C28" s="15" t="inlineStr">
+      <c r="C28" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D28" s="17" t="n">
+      <c r="D28" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="E28" s="18" t="n">
+      <c r="E28" s="28" t="n">
         <v>716</v>
       </c>
-      <c r="F28" s="19" t="n">
+      <c r="F28" s="29" t="n">
         <v>1432</v>
       </c>
-      <c r="G28" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H28" s="16" t="inlineStr">
+      <c r="G28" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H28" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="15" t="n">
+      <c r="A29" s="23" t="n">
         <v>25</v>
       </c>
-      <c r="B29" s="16" t="inlineStr">
+      <c r="B29" s="24" t="inlineStr">
         <is>
           <t>FILTRO SODRAMAR FM-36 – COM 40kg areia</t>
         </is>
       </c>
-      <c r="C29" s="15" t="inlineStr">
+      <c r="C29" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D29" s="17" t="n">
+      <c r="D29" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="E29" s="18" t="n">
+      <c r="E29" s="28" t="n">
         <v>714</v>
       </c>
-      <c r="F29" s="19" t="n">
+      <c r="F29" s="29" t="n">
         <v>1428</v>
       </c>
-      <c r="G29" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H29" s="16" t="inlineStr">
+      <c r="G29" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H29" s="24" t="inlineStr">
         <is>
           <t>wf-aquarius</t>
         </is>
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="n">
+      <c r="A30" s="23" t="n">
         <v>26</v>
       </c>
-      <c r="B30" s="16" t="inlineStr">
+      <c r="B30" s="24" t="inlineStr">
         <is>
           <t>Bomba BMC-75 T.U. 3/4 cv p/ piscinas de até 78 mil litros</t>
         </is>
       </c>
-      <c r="C30" s="15" t="inlineStr">
+      <c r="C30" s="23" t="inlineStr">
         <is>
           <t>m</t>
         </is>
       </c>
-      <c r="D30" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E30" s="18" t="n">
+      <c r="D30" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E30" s="28" t="n">
         <v>1194</v>
       </c>
-      <c r="F30" s="19" t="n">
+      <c r="F30" s="29" t="n">
         <v>1194</v>
       </c>
-      <c r="G30" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H30" s="16" t="inlineStr">
+      <c r="G30" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H30" s="24" t="inlineStr">
         <is>
           <t>amalfi-tramonti</t>
         </is>
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="15" t="n">
+      <c r="A31" s="23" t="n">
         <v>27</v>
       </c>
-      <c r="B31" s="16" t="inlineStr">
+      <c r="B31" s="24" t="inlineStr">
         <is>
           <t>Coadeira modelo Padrão – Sodramar</t>
         </is>
       </c>
-      <c r="C31" s="15" t="inlineStr">
+      <c r="C31" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D31" s="17" t="n">
+      <c r="D31" s="27" t="n">
         <v>1.5</v>
       </c>
-      <c r="E31" s="18" t="n">
+      <c r="E31" s="28" t="n">
         <v>785</v>
       </c>
-      <c r="F31" s="19" t="n">
+      <c r="F31" s="29" t="n">
         <v>1177.5</v>
       </c>
-      <c r="G31" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H31" s="16" t="inlineStr">
+      <c r="G31" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H31" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="15" t="n">
+      <c r="A32" s="23" t="n">
         <v>28</v>
       </c>
-      <c r="B32" s="16" t="inlineStr">
+      <c r="B32" s="24" t="inlineStr">
         <is>
           <t>FILTRO SODRAMAR FM-50 – COM 125kg areia</t>
         </is>
       </c>
-      <c r="C32" s="15" t="inlineStr">
+      <c r="C32" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D32" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E32" s="18" t="n">
+      <c r="D32" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E32" s="28" t="n">
         <v>1162</v>
       </c>
-      <c r="F32" s="19" t="n">
+      <c r="F32" s="29" t="n">
         <v>1162</v>
       </c>
-      <c r="G32" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H32" s="16" t="inlineStr">
+      <c r="G32" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H32" s="24" t="inlineStr">
         <is>
           <t>wf-aquarius</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="15" t="n">
+      <c r="A33" s="23" t="n">
         <v>29</v>
       </c>
-      <c r="B33" s="16" t="inlineStr">
+      <c r="B33" s="24" t="inlineStr">
         <is>
           <t>FILTRO DE PISCINA SODRAMAR FM-30</t>
         </is>
       </c>
-      <c r="C33" s="15" t="inlineStr">
+      <c r="C33" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D33" s="17" t="n">
+      <c r="D33" s="27" t="n">
         <v>2</v>
       </c>
-      <c r="E33" s="18" t="n">
+      <c r="E33" s="28" t="n">
         <v>580</v>
       </c>
-      <c r="F33" s="19" t="n">
+      <c r="F33" s="29" t="n">
         <v>1160</v>
       </c>
-      <c r="G33" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H33" s="16" t="inlineStr">
+      <c r="G33" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H33" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="15" t="n">
+      <c r="A34" s="23" t="n">
         <v>30</v>
       </c>
-      <c r="B34" s="16" t="inlineStr">
+      <c r="B34" s="24" t="inlineStr">
         <is>
           <t>Comando para LED com troca de cores, Controle Remoto</t>
         </is>
       </c>
-      <c r="C34" s="15" t="inlineStr">
+      <c r="C34" s="23" t="inlineStr">
         <is>
           <t>un</t>
         </is>
       </c>
-      <c r="D34" s="17" t="n">
+      <c r="D34" s="27" t="n">
         <v>1.5</v>
       </c>
-      <c r="E34" s="18" t="n">
+      <c r="E34" s="28" t="n">
         <v>720</v>
       </c>
-      <c r="F34" s="19" t="n">
+      <c r="F34" s="29" t="n">
         <v>1080</v>
       </c>
-      <c r="G34" s="15" t="n">
-        <v>1</v>
-      </c>
-      <c r="H34" s="16" t="inlineStr">
+      <c r="G34" s="23" t="n">
+        <v>1</v>
+      </c>
+      <c r="H34" s="24" t="inlineStr">
         <is>
           <t>fonseca-empreendimentos-estoril</t>
         </is>
